--- a/YouTube이슈분석_개인채널_2026-07-04.xlsx
+++ b/YouTube이슈분석_개인채널_2026-07-04.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="232">
   <si>
     <t>날짜</t>
   </si>
@@ -63,13 +63,664 @@
   </si>
   <si>
     <t>분석방식</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>한국</t>
+  </si>
+  <si>
+    <t>경제</t>
+  </si>
+  <si>
+    <t>이재용의 저주가 중앙그룹의 돈 줄을 틀어막았다 삼성의 뒤통수를 친 중앙일보의 최후</t>
+  </si>
+  <si>
+    <t>귀에쏙쏙경제학</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>24:51</t>
+  </si>
+  <si>
+    <t>삼성의 지원으로 성장한 중앙그룹(JTBC)이 경영진의 무리한 중계권 투자와 자금난으로 인해 2026년 6월 206억 원의 채무불이행을 선언하고 핵심 계열사 법정관리를 신청했습니다. 과거 삼성과 이재용 회장에 대해 비판적 태도를 보였던 이들의 몰락 과정을 통해 방만한 경영과 대규모 투자 실패가 기업에 미치는 치명적인 결과를 심층 분석합니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 자극적인 제목과 배신 서사를 강조한 클릭베이트 성격이 강하므로, 기업 재무 상태를 확인할 때는 감정적인 프레임보다 실제 공시 자료와 재무제표를 바탕으로 객관적으로 판단해야 합니다.</t>
+  </si>
+  <si>
+    <t>▶</t>
+  </si>
+  <si>
+    <t>메타데이터+자막(Gemini)</t>
+  </si>
+  <si>
+    <t>호남 반도체 프로젝트 삼전닉스 투자, 인프라까지 완벽정리!</t>
+  </si>
+  <si>
+    <t>장르만 여의도</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>59:53</t>
+  </si>
+  <si>
+    <t>본 영상은 삼성전자와 SK하이닉스가 주도하는 4,700조 원 규모의 반도체 메가 프로젝트의 성사 배경과 투자 계획을 분석합니다. 핵심 인프라인 전력, 용수, 인재 확보 방안을 점검하고, 최근 AI 반도체 시장의 조정 국면과 '칩플레이션' 현상이 산업에 미칠 영향을 전문가들이 심도 있게 토론합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 4,700조 원이라는 막대한 투자 금액의 실체와 현실적인 인프라 구축 가능성을 냉철하게 비교하며 시청하면 투자 흐름 파악에 도움이 됩니다.</t>
+  </si>
+  <si>
+    <t>[지식뉴스] "AI 데이터센터, 이제 한국으로 몰려온다'"..빅테크가 앞다퉈 한국을 새 거점으로 점찍은 진짜 이유 (ft.조홍종 단국대 경제학과 교수) / 교양이를 부탁해</t>
+  </si>
+  <si>
+    <t>교양이를 부탁해</t>
+  </si>
+  <si>
+    <t>24:20</t>
+  </si>
+  <si>
+    <t>본 영상은 AI 시대를 맞아 반도체만큼 중요해진 '전력'의 가치를 조명합니다. 미국 중심의 에너지 패권 변화 속에서 데이터센터와 제조업에 필수적인 전력 수급 문제와 한국의 전력 인프라 경쟁력을 분석합니다. 한국이 원전 및 전력기기 산업을 통해 글로벌 전력 시장에서 기회를 선점하고, 이를 통해 국가적 생존 전략을 어떻게 모색해야 하는지를 심도 있게 다룹니다.</t>
+  </si>
+  <si>
+    <t>⚠️ AI 시대의 핵심은 반도체만이 아닌 전력망임을 이해해야 향후 글로벌 산업 지형과 투자 기회를 정확히 파악할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>재테크</t>
+  </si>
+  <si>
+    <t>한국 아파트 싹 다 물갈이 된다, 2027년부터 집값 무서울 겁니다 (김진 앵커 풀버전)</t>
+  </si>
+  <si>
+    <t>김작가 TV</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>1:28:28</t>
+  </si>
+  <si>
+    <t>본 영상은 김진 앵커가 출연하여 한국 부동산 시장의 변화와 향후 집값 전망을 분석하는 내용을 담고 있습니다. 아파트 시장의 대대적인 변화가 예고된 2027년을 기점으로 주거 환경과 가격 변동성이 커질 것으로 예측하며, 부동산 시장의 흐름과 자산 가치 변화에 따른 대응 전략을 심도 있게 다룹니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목을 사용한 클릭베이트 요소가 있으므로, 특정 종목이나 정책에 대한 맹신보다는 거시적인 경제 흐름과 시장의 논리를 냉정하게 판단해야 합니다.</t>
+  </si>
+  <si>
+    <t>국민연금이 팔기 시작했다, 이거 모르면 큰일 난다</t>
+  </si>
+  <si>
+    <t>재테크읽어주는 파일럿</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>9:53</t>
+  </si>
+  <si>
+    <t>재테크읽어주는 파일럿 채널에서 발행하는 미국 주식 비법서 출간 소식과 예약 구매 혜택을 알리는 영상입니다. 7월 8일부터 발송되는 신간의 내용과 더불어, 2권 세트 구매 시 대한항공 퍼스트클래스 왕복 항공권 이벤트에 자동 응모되는 내용을 포함하고 있습니다. 구독자들의 투자 성과를 돕기 위한 책임을 강조하며, 관심 있는 이들에게 예약 구매를 독려하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 투자 도서 홍보 영상이므로 실질적인 시장 분석보다 판매 정보 위주임을 인지하고 구매를 결정해야 합니다.</t>
+  </si>
+  <si>
+    <t>부동산 추가 규제 나왔다, 앞으로 집값 이렇게 됩니다</t>
+  </si>
+  <si>
+    <t>부읽남TV_내집마련부터건물주까지</t>
+  </si>
+  <si>
+    <t>21:18</t>
+  </si>
+  <si>
+    <t>본 영상은 정부의 기습적인 부동산 추가 규제 발표에 따른 시장 영향과 향후 집값 전망을 분석합니다. 새로운 규제가 즉시 시행됨에 따라 시장의 불확실성이 커진 상황에서, 실거주자 및 투자자가 정책 변화를 어떻게 해석하고 자산 가치를 지켜야 할지에 대한 대응 전략을 다룹니다.</t>
+  </si>
+  <si>
+    <t>⚠️부동산 규제는 시장 흐름을 즉각적으로 변화시키므로, 발표 직후 정책의 세부 조항을 확인하고 실거주 목적인지 투자 목적인지에 따른 맞춤형 포트폴리오 재점검이 필수입니다.</t>
+  </si>
+  <si>
+    <t>자기계발</t>
+  </si>
+  <si>
+    <t>허경환이랑 프랑스 여행 계획 짜기 1일차 (파리민수, 영어공부법, 고민상담)</t>
+  </si>
+  <si>
+    <t>악성 내성인 정일영</t>
+  </si>
+  <si>
+    <t>19:31</t>
+  </si>
+  <si>
+    <t>유튜버 정일영이 개그맨 허경환을 만나 프랑스 여행 계획을 세우며 인생 고민을 나누는 영상입니다. 허경환은 외국어 공부를 계속 미루는 자신의 고민을 털어놓고, 정일영은 이에 대한 조언과 함께 예능 선배로서의 노하우를 전수합니다. 두 사람의 진솔한 대화와 훈훈한 케미를 담고 있으며, 다음 편에는 황치열이 출연할 것을 예고하며 기대감을 높였습니다.</t>
+  </si>
+  <si>
+    <t>외국어 공부를 계속 미루고 있다면 정일영이 제시하는 프랑스어 박사만의 구체적인 학습 전략을 참고해 보세요.</t>
+  </si>
+  <si>
+    <t>헬스터디 이채연이 알려주는 국어 공부법</t>
+  </si>
+  <si>
+    <t>이채연</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>헬스터디 출연자 이채연이 수험생들을 위해 자신의 국어 공부법을 공유하는 영상입니다. 기초적인 학습 방향성을 제시하며, 시청자들의 궁금증을 해결하기 위해 곧 2탄 영상을 올릴 것임을 예고했습니다. 수능 국어 성적 향상을 고민하는 학생들에게 실질적인 가이드를 제공합니다.</t>
+  </si>
+  <si>
+    <t>구체적인 공부 방법론은 곧 업로드될 2탄 영상을 통해 더욱 상세히 확인할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>잘되는 아이들 주변에는 꼭 ‘이런 어른’들이 있습니다 ㅣ Ep. 사람산책 14 (최재천 교수님 1부)</t>
+  </si>
+  <si>
+    <t>책과삶</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>26:48</t>
+  </si>
+  <si>
+    <t>최재천 교수가 출연하여 '선한 야망'을 주제로 삶의 태도와 교육관을 논합니다. 능력주의 사회의 위험성을 경고하고, 나이 듦에 따른 품격, 좋아하는 일의 가치, 그리고 자녀를 성장시키는 부모의 역할에 대해 통찰력 있는 조언을 건넵니다.</t>
+  </si>
+  <si>
+    <t>자녀를 성공으로 이끌고 싶다면 성취를 강요하기보다 스스로 좋아하는 일을 찾고 몰입할 수 있도록 돕는 어른이 되어야 합니다.</t>
+  </si>
+  <si>
+    <t>게임</t>
+  </si>
+  <si>
+    <t>혜안져스 "메차 카멜레온" 이제 쥰내 잘합니다ㅋㅋㅋㅋㅋㅋ🔥</t>
+  </si>
+  <si>
+    <t>혜안</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>29:49</t>
+  </si>
+  <si>
+    <t>유튜버 혜안이 멤버들과 함께 '메타 카멜레온' 게임을 플레이하며 펼치는 유쾌한 상황을 담은 영상입니다. 초반에는 서툴렀던 실력이 점차 향상되어 능숙하게 게임을 즐기는 과정을 보여주며, 특유의 티키타카와 재치 있는 입담을 통해 시청자들에게 큰 웃음을 선사합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 클릭베이트성 제목을 활용한 예능형 콘텐츠이므로, 게임 실력 그 자체보다는 출연진 간의 재미있는 상황극과 리액션을 위주로 감상하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>저는 저를 숨겼습니다</t>
+  </si>
+  <si>
+    <t>랄로</t>
+  </si>
+  <si>
+    <t>47:24</t>
+  </si>
+  <si>
+    <t>유튜버 랄로가 자신의 과거와 솔직한 내면을 고백하는 영상입니다. 그동안 대중 앞에 자신의 진짜 모습을 숨기고 가식적으로 행동해왔던 점을 인정하며, 시청자들에게 느끼는 부채감과 앞으로 진정성 있는 태도로 소통하고 싶다는 개인적인 다짐을 담담하게 이야기합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 달리 실제 영상은 인간적인 고뇌와 진솔한 심경 고백이 중심이 되는 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>역전극 [T1scord 2026 vs GEN]</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>20:48</t>
+  </si>
+  <si>
+    <t>T1의 공식 유튜브 채널에 업로드된 영상으로, T1 선수들과 젠지(GEN) 간의 긴장감 넘치는 경기 내용을 다룬 역전극 콘텐츠입니다. 선수들의 경기력과 팀워크를 엿볼 수 있으며, 다음 일정으로 TLAW 및 KC전 업로드 소식을 함께 전하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ T1 선수들의 생생한 개인 방송을 시청하고 싶다면 설명란에 기재된 공식 숲(SOOP) 방송국 링크를 통해 확인해 보세요.</t>
+  </si>
+  <si>
+    <t>IT·테크</t>
+  </si>
+  <si>
+    <t>긴급속보 | 애플, 최소 20만원 넘게 가격 올려버렸다? 갑자기 이런 미친 결정을 한 진짜 이유</t>
+  </si>
+  <si>
+    <t>ITSub잇섭</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>12:18</t>
+  </si>
+  <si>
+    <t>애플이 2026년 6월 25일부로 대부분의 제품군 가격을 최소 5.7%에서 최대 54.3%까지 기습 인상했습니다. 잇섭은 이번 인상의 배경으로 최근 지속되는 글로벌 메모리 부족 사태를 지목하며, 제품별 구체적인 인상 폭과 함께 한국 시장의 위상 및 애플의 가격 정책 변화에 대해 심도 있게 분석했습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 갑작스러운 대규모 가격 인상은 글로벌 부품 수급 상황과 밀접한 연관이 있으므로, 애플 제품 구매 전 해당 시점의 부품 단가 변동 이슈를 미리 확인하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>플레이스토어가 나를 감시한다고? 갤럭시폰에서  ‘이 버튼’ 당장 끄고 개인정보와 스마트폰 배터리 둘 다 잡으세요!</t>
+  </si>
+  <si>
+    <t>시니어정보 양쌤</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>본 영상은 갤럭시 스마트폰 사용자가 배터리 소모를 줄이고 개인정보를 보호할 수 있는 필수 설정법을 안내합니다. 구글 플레이스토어의 데이터 수집 차단, 위치 정보 및 진단 데이터 전송 해제, 안드로이드 맞춤형 서비스 중단 등 실제 화면을 보며 따라 할 수 있는 최적화 과정을 상세히 다루어 스마트폰 성능 향상과 보안 강화를 돕습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 불필요한 데이터 전송 설정을 끄는 것만으로도 스마트폰의 발열을 줄이고 배터리 수명을 효과적으로 연장할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>요즘 13만원짜리 게임기 RG 로테이트 수준</t>
+  </si>
+  <si>
+    <t>UNDERkg</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>UNDERkg이 리뷰한 13만 원대 안드로이드 게임기 RG 로테이트는 화면이 90도 회전하며 게임패드가 나타나는 독특한 구조가 특징입니다. 합리적인 가격대와 준수한 인터페이스, 조작감을 갖췄으나 L2/R2 버튼의 조작성과 진동 모터 위치, 조도 센서 부재 등 몇 가지 아쉬운 마감이 존재합니다.</t>
+  </si>
+  <si>
+    <t>저렴한 가격에 독특한 폼팩터를 경험할 수 있지만, L2/R2 버튼의 불편함과 기능적 마감 부족을 미리 인지하고 구매를 결정하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>라이프</t>
+  </si>
+  <si>
+    <t>일본 오사카에서 어깨빵하는 빌런 참교육 하는 육은영쌤</t>
+  </si>
+  <si>
+    <t>매드브로 MadBros</t>
+  </si>
+  <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>본 영상은 유튜브 채널 '매드브로'의 콘텐츠로, 일본 오사카 여행 중 길거리에서 의도적으로 어깨를 부딪치며 위협을 가하는 이른바 '어깨빵 빌런'을 만난 육은영쌤이 이를 당당하게 대처하고 참교육하는 과정을 담고 있습니다. 영상은 여행지에서의 돌발 상황에 대한 긴장감과 이를 슬기롭게 해결하는 과정을 통해 시청자들에게 카타르시스를 제공하며, 중간에 냉각 손선풍기 광고가 포함되어 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 해당 영상은 갈등 상황을 연출하거나 자극적인 요소를 활용한 클릭베이트성 콘텐츠일 수 있으므로 재미 위주로 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>100시간 동안 세계에서 가장 오염된 도시에서 살면 생기는 일</t>
+  </si>
+  <si>
+    <t>고재영</t>
+  </si>
+  <si>
+    <t>45:14</t>
+  </si>
+  <si>
+    <t>유튜버 고재영이 세계에서 가장 공기가 나쁜 것으로 알려진 도시에서 100시간 동안 직접 거주하며 겪는 생존기와 현지의 대기 오염 실태를 다룬 영상입니다. 극심한 대기 오염 속에서 신체적 변화와 현지인들의 생활상을 관찰하며 환경 문제의 심각성을 생생하게 전달합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목과 썸네일은 시청자의 호기심을 유도하는 자극적인 요소를 포함하고 있으므로, 정보성보다는 체험형 예능 콘텐츠로 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>아들이랑 둘이사는 서인영 절친 싱글맘 조민아 집 최초공개 (+오해와 진실)</t>
+  </si>
+  <si>
+    <t>개과천선 서인영</t>
+  </si>
+  <si>
+    <t>29:23</t>
+  </si>
+  <si>
+    <t>서인영이 절친 조민아의 집을 방문하여 쥬얼리 시절 겪었던 과거의 오해를 풀고 진솔한 대화를 나누는 모습을 담았습니다. 아들과 함께 홀로 육아를 이어가는 조민아의 일상을 공개하며, 두 사람이 오랜만에 회포를 풀고 변치 않는 우정을 확인하는 따뜻한 시간을 보여줍니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 갈등 해소를 기대하기보다는 쥬얼리 멤버들의 과거 서사와 싱글맘 조민아의 근황을 확인하는 데 초점이 맞춰진 브이로그입니다.</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>【元テレ東×元朝日新聞対談】新聞とテレビは終わるのか？朝日毎日読売の生存戦略／ネット時代の「有料課金」は日経一人勝ちか？／AI時代求められるのは「誰が言っているか」【下矢一良×今野忍】｜選挙ドットコム</t>
+  </si>
+  <si>
+    <t>選挙ドットコムちゃんねる</t>
+  </si>
+  <si>
+    <t>1:03:15</t>
+  </si>
+  <si>
+    <t>전직 TV도쿄 디렉터이자 PR 전문가인 시모야 카즈요시와 아사히신문 정치부 기자 콘노 시노부가 대담을 나눕니다. 급변하는 미디어 환경 속에서 신문과 방송의 생존 전략을 논하고, 닛케이신문의 유료화 성공 사례와 AI 시대에 필요한 신뢰성 있는 정보의 중요성을 심층적으로 분석합니다.</t>
+  </si>
+  <si>
+    <t>전통 언론 매체가 디지털 전환 시대에 어떻게 영향력을 유지하고 유료 비즈니스 모델을 구축해야 하는지에 대한 업계 전문가의 시각을 확인할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>また韓国市場の暴落がAI関連へ波及！米軍がイランに対し空爆を実施！【6/27 米国株ニュース】</t>
+  </si>
+  <si>
+    <t>とも米国株投資チャンネル</t>
+  </si>
+  <si>
+    <t>15:19</t>
+  </si>
+  <si>
+    <t>본 영상은 한국 증시의 급락세가 AI 관련주로 확산하는 현상과 미군의 이란 공습 소식을 다룹니다. 글로벌 지정학적 리스크와 특정 시장의 하락이 미국 증시에 미치는 잠재적 영향력을 분석하며, 투자자들에게 시장 변동성에 대비한 리스크 관리의 중요성을 강조하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목에 자극적인 이슈를 언급하여 클릭을 유도하고 있으므로, 실제 뉴스 원문을 교차 확인하여 투자 결정 시 감정적 대응을 자제해야 합니다.</t>
+  </si>
+  <si>
+    <t>資産1000万円超えると人生が激変する理由</t>
+  </si>
+  <si>
+    <t>高須幹弥（高須クリニック）</t>
+  </si>
+  <si>
+    <t>20:31</t>
+  </si>
+  <si>
+    <t>다카스 미키야 원장이 자산 1,000만 엔을 넘기는 순간 삶이 어떻게 변화하는지 설명합니다. 심리적 여유가 생기며 선택의 폭이 넓어지고, 자본주의 사회에서 돈이 주는 심리적 안정감과 자신감이 인생을 긍정적인 방향으로 이끄는 원동력이 됨을 강조합니다.</t>
+  </si>
+  <si>
+    <t>⚠️자산 1,000만 엔은 단순한 숫자가 아니라 인생의 선택권을 넓히고 심리적 안정감을 확보하는 중요한 전환점입니다.</t>
+  </si>
+  <si>
+    <t>【元手200万→10億円】キオクシアだけを見るな！次の注目はTOPIX？／新NISA「最初の3000万円」がカギ／億を目指す4つの投資方法《上岡正明》</t>
+  </si>
+  <si>
+    <t>楽待 RAKUMACHI</t>
+  </si>
+  <si>
+    <t>53:57</t>
+  </si>
+  <si>
+    <t>본 영상은 자산 10억 엔을 달성한 투자자 카미오카 마사아키가 출연해 초기 자산 200만 엔에서 시작한 투자 철학을 공유합니다. 자산 3,000만 엔까지는 복리 효과가 크지 않아 공격적 투자가 필요하며, 신NISA 제도를 활용한 자산 배분 전략과 폭락장에 대비하는 투자자의 마음가짐 및 구체적인 핵심 자산 운용법을 다룹니다.</t>
+  </si>
+  <si>
+    <t>⚠️자산 3,000만 엔 구간을 돌파하는 것이 투자의 임계점이며, 이를 넘어서야 복리 효과를 통한 자산 증식이 가속화됩니다.</t>
+  </si>
+  <si>
+    <t>退職後に2億円全力投資、お金が減るとこうなる【資産公開】</t>
+  </si>
+  <si>
+    <t>S&amp;P500最強伝説</t>
+  </si>
+  <si>
+    <t>37:52</t>
+  </si>
+  <si>
+    <t>은퇴 후 2억 엔이라는 거액의 자산을 S&amp;P500 중심의 투자 상품에 올인한 유튜버가 시장 변동성에 따른 자산 감소 과정을 솔직하게 공개하는 영상입니다. 고액 투자자가 겪는 심리적 압박과 자산 변동의 현실을 가감 없이 보여주며, 장기 투자 관점에서의 자산 운용 전략과 마인드셋을 다룹니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 거액을 한 번에 투자하는 전략은 시장 하락기 심리적 고통이 극심하므로 자신의 리스크 감당 능력을 객관적으로 파악하는 것이 우선입니다.</t>
+  </si>
+  <si>
+    <t>【全紹介】1〜100までの全素数の倍数判定法あなたは知っていますか？</t>
+  </si>
+  <si>
+    <t>日常でんがん</t>
+  </si>
+  <si>
+    <t>10:18</t>
+  </si>
+  <si>
+    <t>본 영상은 유튜버 뎅간이 운영하는 '일상 뎅간' 채널의 소개 영상입니다. 과거 '하나오뎅간' 채널을 운영했던 경험을 바탕으로, 현재는 혼자서 공부 방법론과 수학 해설 등 교육 콘텐츠를 중심으로 활동하고 있음을 밝힙니다. 또한 자신의 학습 경험을 담은 저서 '원래 바보였던 사람에 의한 바보를 위한 공부 100조'를 홍보하며, 시청자들과 소통하고 학습 동기를 부여하는 활동에 주력하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 학습 효율을 높이고 싶은 학생이라면 뎅간이 출간한 공부법 책을 통해 저자의 구체적인 학습 노하우를 참고해 보세요.</t>
+  </si>
+  <si>
+    <t>院生vlog🫙勉強無し生活に困惑 | 社会人になる準備 | パース, ロットネスト島旅🚢 《オーストラリア》</t>
+  </si>
+  <si>
+    <t>Okisvlog</t>
+  </si>
+  <si>
+    <t>27:37</t>
+  </si>
+  <si>
+    <t>대학원 졸업 후 사회인 입사 전, 호주 퍼스에서의 여유로운 일상을 담은 브이로그입니다. 쿼카가 있는 로트네스트 섬 여행과 요리, 베이킹, 컬러링 등을 하며 자신을 돌아보는 시간을 갖습니다. 일본 귀국 후 바쁜 이사 및 행정 절차를 앞두고 온전한 쉼을 즐기는 모습과 함께, 새로운 시작을 준비하는 차분한 마음가짐을 공유합니다.</t>
+  </si>
+  <si>
+    <t>사회인 입사 전의 막막한 공백기를 불안해하기보다, 자신만의 속도로 일상을 채우며 온전히 재충전하는 시간을 갖는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>【受験の天王山が始まる...】前に必ず見てほしい高3向け"7月の勉強法"を解説します。</t>
+  </si>
+  <si>
+    <t>河野塾チャンネル</t>
+  </si>
+  <si>
+    <t>6:16</t>
+  </si>
+  <si>
+    <t>본 영상은 입시의 승부처인 7월을 앞둔 고3 수험생을 위해 고노 겐토가 이끄는 고노 학원 강사진이 제안하는 효율적인 학습 전략을 다룹니다. 여름방학 전 기초를 확실히 다지고 공통 테스트 대비 모의고사를 적극 활용하여 자신의 약점을 파악하고 성적 향상을 이룰 수 있는 구체적인 학습 방향과 여름 캠페인 정보를 상세히 설명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 입시의 승부처인 7월에 자신의 객관적인 위치를 파악하고 취약점을 보완하는 것이 수험 생활의 성패를 가르는 핵심입니다.</t>
+  </si>
+  <si>
+    <t>음악</t>
+  </si>
+  <si>
+    <t>「瞬間ジャーニー」 Music Video ／ TOP4(キヨ・レトルト・牛沢・ガッチマン)</t>
+  </si>
+  <si>
+    <t>キヨ。</t>
+  </si>
+  <si>
+    <t>3:49</t>
+  </si>
+  <si>
+    <t>본 영상은 인기 게임 실황자 그룹 TOP4(키요, 레토르트, 우시자와, 갓치만)가 발표한 곡 '순간 저니(瞬間ジャーニー)'의 공식 뮤직비디오입니다. ORANGE RANGE의 HIROKI와 NAOTO가 각각 작사와 작곡을 맡아 화제를 모았으며, 4인의 유쾌한 매력과 청량한 분위기가 돋보이는 곡입니다.</t>
+  </si>
+  <si>
+    <t>6월 27일부터 주요 음악 스트리밍 플랫폼에서 정식 음원 감상이 가능합니다.</t>
+  </si>
+  <si>
+    <t>IS:SUE (イッシュ) 'come again' (Original by m-flo) Live Performance [2026.06.19 REBORN Collection 2026]</t>
+  </si>
+  <si>
+    <t>IS:SUE</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>5:04</t>
+  </si>
+  <si>
+    <t>본 영상은 걸그룹 IS:SUE(이슈)가 2026년 6월 19일 개최된 'REBORN Collection 2026' 무대에서 선보인 m-flo의 히트곡 'come again' 라이브 퍼포먼스 영상입니다. 세련된 퍼포먼스와 멤버들의 가창력이 돋보이며, 영상 설명란을 통해 정규 1집 'QUARTET' 정보 및 2번째 투어 개최 소식 등 그룹의 최신 활동 정보를 함께 확인할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>영상 설명란의 링크를 통해 IS:SUE의 1집 앨범 'QUARTET' 정보와 다가오는 2번째 투어 일정 등 공식 활동 소식을 미리 확인해 보세요.</t>
+  </si>
+  <si>
+    <t>1人で新作リズム天国を先行プレイして俺より壊れてる奴いんの？</t>
+  </si>
+  <si>
+    <t>1:40:35</t>
+  </si>
+  <si>
+    <t>유명 게임 실황자 키요(キヨ。)가 닌텐도의 신작 '리듬천국 미라클 스타즈'를 선행 플레이하는 영상입니다. 특유의 에너지 넘치는 진행과 함께 리듬 게임 특유의 박자감과 코믹한 리액션을 보여주며, 시청자들에게 게임의 재미와 분위기를 생생하게 전달합니다. 닌텐도의 공식 협력을 받아 제작되었으며, 게임의 독특한 리듬 메커니즘을 경험하며 즐거워하는 모습이 담겨 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 게임의 고난도 리듬 패턴을 플레이할 때 박자를 놓치지 않으려면 배경음악의 베이스 음을 듣는 것이 도움이 됩니다.</t>
+  </si>
+  <si>
+    <t>【マインクラフト】地下の強制労働施設で埋蔵金を探すことになりました【日常組】</t>
+  </si>
+  <si>
+    <t>日常組</t>
+  </si>
+  <si>
+    <t>1:34:58</t>
+  </si>
+  <si>
+    <t>일상조(日常組) 멤버 4명이 마인크래프트 내의 지하 강제 노동 시설에 갇혀 매장금을 찾아 탈출하기 위해 분투하는 게임 실황 영상입니다. 독특한 맵 환경 속에서 멤버 특유의 유머러스한 티키타카와 협동 과정을 통해 상황을 해결해 나가는 재미를 선사합니다.</t>
+  </si>
+  <si>
+    <t>일상조 멤버 간의 케미스트리와 만담이 주된 재미 요소이므로, 자막을 통해 대화의 흐름을 따라가면 더욱 즐겁게 시청할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>【4人】「全員一致ゲーム＆全員不一致ゲーム」で連続目指したら地獄でした</t>
+  </si>
+  <si>
+    <t>レトルト</t>
+  </si>
+  <si>
+    <t>52:53</t>
+  </si>
+  <si>
+    <t>인기 실황자 레토르트, 키요, 우시자와, 가치맨 4인이 모여 '전원 일치 게임'과 '전원 불일치 게임'에 도전하는 영상입니다. 연속 성공을 목표로 고군분투하지만, 서로의 의견이 엇갈리며 발생하는 엉뚱한 상황과 예기치 못한 실패 과정이 큰 웃음을 자아냅니다. 기존에 공개되지 않았던 미공개 영상을 모아 편집한 기획물로, 멤버들의 완벽하지 않은 호흡이 오히려 재미 포인트가 됩니다.</t>
+  </si>
+  <si>
+    <t>멤버 간의 독특한 사고방식 차이를 확인하며 즐기면 더욱 재미있게 시청할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>【今すぐオフ】Googleアカウントの新しいプライバシー設定と3つの変更点をわかりやすく解説！【2026年6月～】</t>
+  </si>
+  <si>
+    <t>スマホのコンシェルジュ「株式会社コアコンシェル」</t>
+  </si>
+  <si>
+    <t>9:20</t>
+  </si>
+  <si>
+    <t>Google이 발표한 새로운 개인정보 보호 정책 변경 사항을 다룹니다. 2026년 6월부터 적용되는 검색 서비스 기록과 미디어 저장 방식의 변화를 상세히 설명하며, 사용자가 데이터 관리와 개인화 설정을 스스로 제어할 수 있도록 돕는 구체적인 설정 변경 가이드를 제공합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 구글 계정의 데이터 수집과 개인화 설정을 유지하고 싶지 않다면 영상에서 안내하는 '미디어 저장' 및 '검색 서비스 기록' 설정을 지금 바로 확인하여 해제하십시오.</t>
+  </si>
+  <si>
+    <t>【ルームツアー?】自宅にクソでかサーバーを作ったYouTuberがいるらしいので調査してきました。</t>
+  </si>
+  <si>
+    <t>TECH WORLD</t>
+  </si>
+  <si>
+    <t>25:48</t>
+  </si>
+  <si>
+    <t>IT 유튜버 TECH WORLD가 '운차마(うんちゃま)'의 자택을 방문하여 구축해 놓은 거대한 서버실을 소개하는 영상입니다. 일반 가정집에서는 보기 힘든 고성능 서버 환경과 인프라 구성을 상세히 보여주며, 개인 서버 운영에 관심 있는 엔지니어들에게 흥미로운 볼거리를 제공합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 가정 내에 고성능 서버를 구축할 때는 전력 소모량과 소음, 그리고 발열 관리를 위한 냉방 설비가 필수적으로 고려되어야 합니다.</t>
+  </si>
+  <si>
+    <t>【検証】新型「REDMAGIC 11”S” Pro」を購入。”怪しい動作”どうなった？</t>
+  </si>
+  <si>
+    <t>さいちょう2nd</t>
+  </si>
+  <si>
+    <t>본 영상은 게이밍 스마트폰인 'REDMAGIC 9S Pro'의 검증기로, 이전 모델에서 제기되었던 기기 작동의 의문점들이 최신 모델에서 어떻게 개선되거나 변화했는지를 다루고 있습니다. 게임 성능 중심의 기기 특성을 고려하여 실제 사용 시의 안정성과 소프트웨어 최적화 상태를 사용자 관점에서 객관적으로 분석하는 내용을 담고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 기기 구매 전 의문이 드는 동작이나 소프트웨어 이슈가 있다면 공식 업데이트 기록이나 사용자 커뮤니티의 실사용 후기를 먼저 확인하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>溝口さんに「それ違います」と正直に伝えました</t>
+  </si>
+  <si>
+    <t>ヤマト リノ 本物</t>
+  </si>
+  <si>
+    <t>1:05:52</t>
+  </si>
+  <si>
+    <t>야마토 리노가 기존 10만 구독자 메인 채널을 해킹당해 복구가 불투명해지자, 새로운 채널을 개설하며 구독을 간곡히 요청하는 영상입니다. 시청자들에게 신규 채널로의 이전과 구독을 부탁하며 향후 활동 재개 의지를 밝혔습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 채널 해킹 상황을 알리며 구독을 유도하는 방식의 영상이므로 콘텐츠의 진위 여부를 확인하며 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>【石川県金沢】酔った勢いで旅行したら、過去最悪の空気の旅行が仕上がりました。</t>
+  </si>
+  <si>
+    <t>うじとうえだ</t>
+  </si>
+  <si>
+    <t>2:18:07</t>
+  </si>
+  <si>
+    <t>술기운에 충동적으로 떠난 이시카와현 가나자와 여행에서 예민하고 결벽증이 심한 사장 우지하라와 그를 놀리기 좋아하는 카메라맨 우에다, 친구 사카모토가 겪는 최악의 여행기를 담았습니다. 세 사람의 티격태격하는 갈등과 웃픈 상황이 반복되며, 준비되지 않은 즉흥 여행이 어떻게 파국으로 치닫는지 여과 없이 보여주는 코믹 다큐멘터리입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 계획 없는 충동 여행이 예민한 성격의 동행자와 만났을 때 벌어질 수 있는 최악의 상황을 다루고 있으니 여행 전 멤버 간의 성향 파악은 필수입니다.</t>
+  </si>
+  <si>
+    <t>라이징스타</t>
+  </si>
+  <si>
+    <t>【大谷翔平・佐々木朗希】ドジャース逆転で圧勝！佐々木6失点直後に大谷選手のまさかの発言でプライアーコーチ感銘…マンシー、ベッツ、ラッシング、レジェンドも語る…</t>
+  </si>
+  <si>
+    <t>大谷翔平レジェンド</t>
+  </si>
+  <si>
+    <t>20:06</t>
+  </si>
+  <si>
+    <t>본 영상은 오타니 쇼헤이와 사사키 로키에 관한 최근 MLB 소식을 다룹니다. 다저스의 역전승 과정과 사사키 로키의 6실점 부진에 대한 현지 반응, 특히 경기 중 오타니가 보인 행동에 대한 프라이어 코치의 감명과 동료 선수들의 인터뷰 내용을 중심으로 오타니의 영향력을 집중 조명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 채널은 다수의 스포츠 채널이 사용하는 자극적인 클릭베이트 형식의 콘텐츠를 제공하므로 정보의 출처를 반드시 확인하시기 바랍니다.</t>
+  </si>
+  <si>
+    <t>"홈런 폭격중인 한국 초특급 유망주" 콜업 후 8경기 5홈런에 MVP 선정되자 뒤집어진 미국 현지중계진 ㄷㄷ</t>
+  </si>
+  <si>
+    <t>라인업 스포츠[Line-Up]</t>
+  </si>
+  <si>
+    <t>8:40</t>
+  </si>
+  <si>
+    <t>미국 마이너리그에서 활약 중인 한국 야구 유망주 조원빈 선수가 콜업 후 8경기에서 5개의 홈런을 몰아치며 MVP를 수상하는 압도적인 퍼포먼스를 선보였습니다. 이 소식에 현지 중계진들이 놀라움을 감추지 못하며 극찬을 보내고 있는 상황을 상세히 다루고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목과 썸네일에서 강조하는 '현지 중계진의 반응'은 조회수를 높이기 위한 과장된 자극적 표현이 포함되어 있을 수 있으니 객관적인 기록 위주로 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>ケルチ連絡路が炎上…ロシアは最後の生命線を断たれる一撃に身構える</t>
+  </si>
+  <si>
+    <t>地政学の羅針盤</t>
+  </si>
+  <si>
+    <t>19:23</t>
+  </si>
+  <si>
+    <t>본 영상은 우크라이나가 크림반도를 잇는 핵심 보급로인 케르치 해협의 연료 및 수송 시설을 동시에 타격한 상황을 분석합니다. 러시아는 전방위적인 우크라이나의 압박으로 인해 방어 자원을 분산해야 하는 곤경에 처했으며, 이는 보급선 차단이 전쟁의 판도를 바꿀 수 있음을 시사합니다. 또한 이러한 군사적 흐름이 현대전과 섬나라 방위 전략에 주는 함의를 지정학적 관점에서 다룹니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목과 내용이 자극적인 군사 분석 영상이므로, 객관적인 군사 정세 파악을 위해 여러 소스의 교차 검증이 필요합니다.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,6 +732,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -127,10 +785,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -479,14 +1146,1852 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1260514</v>
+      </c>
+      <c r="J2" s="3">
+        <v>20986</v>
+      </c>
+      <c r="K2" s="3">
+        <v>2327</v>
+      </c>
+      <c r="L2" s="3">
+        <v>123947</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3">
+        <v>275930</v>
+      </c>
+      <c r="J3" s="3">
+        <v>5812</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1909</v>
+      </c>
+      <c r="L3" s="3">
+        <v>59652</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="3">
+        <v>271320</v>
+      </c>
+      <c r="J4" s="3">
+        <v>4658</v>
+      </c>
+      <c r="K4" s="3">
+        <v>438</v>
+      </c>
+      <c r="L4" s="3">
+        <v>42506</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="3">
+        <v>732004</v>
+      </c>
+      <c r="J5" s="3">
+        <v>18064</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1455</v>
+      </c>
+      <c r="L5" s="3">
+        <v>101216</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="3">
+        <v>248130</v>
+      </c>
+      <c r="J6" s="3">
+        <v>8483</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1072</v>
+      </c>
+      <c r="L6" s="3">
+        <v>61701</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="3">
+        <v>331591</v>
+      </c>
+      <c r="J7" s="3">
+        <v>5108</v>
+      </c>
+      <c r="K7" s="3">
+        <v>748</v>
+      </c>
+      <c r="L7" s="3">
+        <v>60873</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8" s="3">
+        <v>217667</v>
+      </c>
+      <c r="J8" s="3">
+        <v>6442</v>
+      </c>
+      <c r="K8" s="3">
+        <v>511</v>
+      </c>
+      <c r="L8" s="3">
+        <v>47089</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="3">
+        <v>65257</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2383</v>
+      </c>
+      <c r="K9" s="3">
+        <v>688</v>
+      </c>
+      <c r="L9" s="3">
+        <v>26552</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="3">
+        <v>177026</v>
+      </c>
+      <c r="J10" s="3">
+        <v>3863</v>
+      </c>
+      <c r="K10" s="3">
+        <v>84</v>
+      </c>
+      <c r="L10" s="3">
+        <v>20279</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="3">
+        <v>645961</v>
+      </c>
+      <c r="J11" s="3">
+        <v>29562</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1799</v>
+      </c>
+      <c r="L11" s="3">
+        <v>301633</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1109175</v>
+      </c>
+      <c r="J12" s="3">
+        <v>9060</v>
+      </c>
+      <c r="K12" s="3">
+        <v>752</v>
+      </c>
+      <c r="L12" s="3">
+        <v>114431</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="2">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="3">
+        <v>233280</v>
+      </c>
+      <c r="J13" s="3">
+        <v>4687</v>
+      </c>
+      <c r="K13" s="3">
+        <v>517</v>
+      </c>
+      <c r="L13" s="3">
+        <v>85110</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="3">
+        <v>711028</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6509</v>
+      </c>
+      <c r="K14" s="3">
+        <v>2471</v>
+      </c>
+      <c r="L14" s="3">
+        <v>79154</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="3">
+        <v>464311</v>
+      </c>
+      <c r="J15" s="3">
+        <v>18948</v>
+      </c>
+      <c r="K15" s="3">
+        <v>2223</v>
+      </c>
+      <c r="L15" s="3">
+        <v>40891</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="N15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="3">
+        <v>120406</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1883</v>
+      </c>
+      <c r="K16" s="3">
+        <v>292</v>
+      </c>
+      <c r="L16" s="3">
+        <v>40118</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3108714</v>
+      </c>
+      <c r="J17" s="3">
+        <v>67753</v>
+      </c>
+      <c r="K17" s="3">
+        <v>11357</v>
+      </c>
+      <c r="L17" s="3">
+        <v>660852</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3389152</v>
+      </c>
+      <c r="J18" s="3">
+        <v>42440</v>
+      </c>
+      <c r="K18" s="3">
+        <v>5869</v>
+      </c>
+      <c r="L18" s="3">
+        <v>406244</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1538989</v>
+      </c>
+      <c r="J19" s="3">
+        <v>32482</v>
+      </c>
+      <c r="K19" s="3">
+        <v>4243</v>
+      </c>
+      <c r="L19" s="3">
+        <v>311099</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="N19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="3">
+        <v>184513</v>
+      </c>
+      <c r="J20" s="3">
+        <v>3130</v>
+      </c>
+      <c r="K20" s="3">
+        <v>289</v>
+      </c>
+      <c r="L20" s="3">
+        <v>23017</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="N20" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="3">
+        <v>41596</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1135</v>
+      </c>
+      <c r="K21" s="3">
+        <v>52</v>
+      </c>
+      <c r="L21" s="3">
+        <v>5195</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="N21" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I22" s="3">
+        <v>495900</v>
+      </c>
+      <c r="J22" s="3">
+        <v>6574</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1761</v>
+      </c>
+      <c r="L22" s="3">
+        <v>67802</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="N22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I23" s="3">
+        <v>207148</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3358</v>
+      </c>
+      <c r="K23" s="3">
+        <v>216</v>
+      </c>
+      <c r="L23" s="3">
+        <v>35937</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="2">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" s="3">
+        <v>206152</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3692</v>
+      </c>
+      <c r="K24" s="3">
+        <v>223</v>
+      </c>
+      <c r="L24" s="3">
+        <v>35928</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="N24" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" s="3">
+        <v>30978</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1245</v>
+      </c>
+      <c r="K25" s="3">
+        <v>81</v>
+      </c>
+      <c r="L25" s="3">
+        <v>5354</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I26" s="3">
+        <v>27370</v>
+      </c>
+      <c r="J26" s="3">
+        <v>716</v>
+      </c>
+      <c r="K26" s="3">
+        <v>70</v>
+      </c>
+      <c r="L26" s="3">
+        <v>5068</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I27" s="3">
+        <v>24085</v>
+      </c>
+      <c r="J27" s="3">
+        <v>625</v>
+      </c>
+      <c r="K27" s="3">
+        <v>34</v>
+      </c>
+      <c r="L27" s="3">
+        <v>4760</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I28" s="3">
+        <v>2038495</v>
+      </c>
+      <c r="J28" s="3">
+        <v>74405</v>
+      </c>
+      <c r="K28" s="3">
+        <v>5204</v>
+      </c>
+      <c r="L28" s="3">
+        <v>293756</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I29" s="3">
+        <v>483348</v>
+      </c>
+      <c r="J29" s="3">
+        <v>22957</v>
+      </c>
+      <c r="K29" s="3">
+        <v>1796</v>
+      </c>
+      <c r="L29" s="3">
+        <v>76741</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1783117</v>
+      </c>
+      <c r="J30" s="3">
+        <v>47972</v>
+      </c>
+      <c r="K30" s="3">
+        <v>4398</v>
+      </c>
+      <c r="L30" s="3">
+        <v>375570</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I31" s="3">
+        <v>636723</v>
+      </c>
+      <c r="J31" s="3">
+        <v>23756</v>
+      </c>
+      <c r="K31" s="3">
+        <v>1013</v>
+      </c>
+      <c r="L31" s="3">
+        <v>243647</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="2">
+        <v>3</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I32" s="3">
+        <v>511786</v>
+      </c>
+      <c r="J32" s="3">
+        <v>15362</v>
+      </c>
+      <c r="K32" s="3">
+        <v>968</v>
+      </c>
+      <c r="L32" s="3">
+        <v>129779</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I33" s="3">
+        <v>335249</v>
+      </c>
+      <c r="J33" s="3">
+        <v>3674</v>
+      </c>
+      <c r="K33" s="3">
+        <v>35</v>
+      </c>
+      <c r="L33" s="3">
+        <v>31824</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I34" s="3">
+        <v>197814</v>
+      </c>
+      <c r="J34" s="3">
+        <v>2866</v>
+      </c>
+      <c r="K34" s="3">
+        <v>154</v>
+      </c>
+      <c r="L34" s="3">
+        <v>20908</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="2">
+        <v>3</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I35" s="3">
+        <v>125639</v>
+      </c>
+      <c r="J35" s="3">
+        <v>4873</v>
+      </c>
+      <c r="K35" s="3">
+        <v>568</v>
+      </c>
+      <c r="L35" s="3">
+        <v>20158</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I36" s="3">
+        <v>1471602</v>
+      </c>
+      <c r="J36" s="3">
+        <v>26227</v>
+      </c>
+      <c r="K36" s="3">
+        <v>11678</v>
+      </c>
+      <c r="L36" s="3">
+        <v>457644</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" s="2">
+        <v>2</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I37" s="3">
+        <v>1326768</v>
+      </c>
+      <c r="J37" s="3">
+        <v>30026</v>
+      </c>
+      <c r="K37" s="3">
+        <v>3094</v>
+      </c>
+      <c r="L37" s="3">
+        <v>373443</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O2" r:id="rId1"/>
+    <hyperlink ref="O3" r:id="rId2"/>
+    <hyperlink ref="O4" r:id="rId3"/>
+    <hyperlink ref="O5" r:id="rId4"/>
+    <hyperlink ref="O6" r:id="rId5"/>
+    <hyperlink ref="O7" r:id="rId6"/>
+    <hyperlink ref="O8" r:id="rId7"/>
+    <hyperlink ref="O9" r:id="rId8"/>
+    <hyperlink ref="O10" r:id="rId9"/>
+    <hyperlink ref="O11" r:id="rId10"/>
+    <hyperlink ref="O12" r:id="rId11"/>
+    <hyperlink ref="O13" r:id="rId12"/>
+    <hyperlink ref="O14" r:id="rId13"/>
+    <hyperlink ref="O15" r:id="rId14"/>
+    <hyperlink ref="O16" r:id="rId15"/>
+    <hyperlink ref="O17" r:id="rId16"/>
+    <hyperlink ref="O18" r:id="rId17"/>
+    <hyperlink ref="O19" r:id="rId18"/>
+    <hyperlink ref="O20" r:id="rId19"/>
+    <hyperlink ref="O21" r:id="rId20"/>
+    <hyperlink ref="O22" r:id="rId21"/>
+    <hyperlink ref="O23" r:id="rId22"/>
+    <hyperlink ref="O24" r:id="rId23"/>
+    <hyperlink ref="O25" r:id="rId24"/>
+    <hyperlink ref="O26" r:id="rId25"/>
+    <hyperlink ref="O27" r:id="rId26"/>
+    <hyperlink ref="O28" r:id="rId27"/>
+    <hyperlink ref="O29" r:id="rId28"/>
+    <hyperlink ref="O30" r:id="rId29"/>
+    <hyperlink ref="O31" r:id="rId30"/>
+    <hyperlink ref="O32" r:id="rId31"/>
+    <hyperlink ref="O33" r:id="rId32"/>
+    <hyperlink ref="O34" r:id="rId33"/>
+    <hyperlink ref="O35" r:id="rId34"/>
+    <hyperlink ref="O36" r:id="rId35"/>
+    <hyperlink ref="O37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -539,7 +3044,162 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I2" s="3">
+        <v>123236</v>
+      </c>
+      <c r="J2" s="3">
+        <v>480</v>
+      </c>
+      <c r="K2" s="3">
+        <v>36</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I3" s="3">
+        <v>83685</v>
+      </c>
+      <c r="J3" s="3">
+        <v>908</v>
+      </c>
+      <c r="K3" s="3">
+        <v>31</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="I4" s="3">
+        <v>77998</v>
+      </c>
+      <c r="J4" s="3">
+        <v>681</v>
+      </c>
+      <c r="K4" s="3">
+        <v>17</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O2" r:id="rId1"/>
+    <hyperlink ref="O3" r:id="rId2"/>
+    <hyperlink ref="O4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/YouTube이슈분석_개인채널_2026-07-04.xlsx
+++ b/YouTube이슈분석_개인채널_2026-07-04.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="227">
   <si>
     <t>날짜</t>
   </si>
@@ -86,10 +86,10 @@
     <t>24:51</t>
   </si>
   <si>
-    <t>삼성의 지원으로 성장한 중앙그룹(JTBC)이 경영진의 무리한 중계권 투자와 자금난으로 인해 2026년 6월 206억 원의 채무불이행을 선언하고 핵심 계열사 법정관리를 신청했습니다. 과거 삼성과 이재용 회장에 대해 비판적 태도를 보였던 이들의 몰락 과정을 통해 방만한 경영과 대규모 투자 실패가 기업에 미치는 치명적인 결과를 심층 분석합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 자극적인 제목과 배신 서사를 강조한 클릭베이트 성격이 강하므로, 기업 재무 상태를 확인할 때는 감정적인 프레임보다 실제 공시 자료와 재무제표를 바탕으로 객관적으로 판단해야 합니다.</t>
+    <t>삼성의 지원을 받던 중앙그룹이 이재용 회장과의 갈등 이후 2026년 JTBC 채무불이행과 계열사 법정관리를 신청하며 몰락했다는 주장입니다. 7,000억 원대 중계권 사업 실패와 외부 자본 유치 과정에서 발생한 경영 위기 및 개인 투자자 피해 등을 다루며, 대기업과 미디어 그룹 간의 관계 변화가 초래한 비극적 결말을 분석하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 자극적인 제목과 허구적 설정을 바탕으로 한 클릭베이트성 콘텐츠일 가능성이 높으므로 정보 수용 시 주의가 필요합니다.</t>
   </si>
   <si>
     <t>▶</t>
@@ -110,10 +110,10 @@
     <t>59:53</t>
   </si>
   <si>
-    <t>본 영상은 삼성전자와 SK하이닉스가 주도하는 4,700조 원 규모의 반도체 메가 프로젝트의 성사 배경과 투자 계획을 분석합니다. 핵심 인프라인 전력, 용수, 인재 확보 방안을 점검하고, 최근 AI 반도체 시장의 조정 국면과 '칩플레이션' 현상이 산업에 미칠 영향을 전문가들이 심도 있게 토론합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 4,700조 원이라는 막대한 투자 금액의 실체와 현실적인 인프라 구축 가능성을 냉철하게 비교하며 시청하면 투자 흐름 파악에 도움이 됩니다.</t>
+    <t>본 영상은 삼성전자와 SK하이닉스를 중심으로 추진되는 4,700조 원 규모의 대규모 반도체 메가 프로젝트의 배경과 투자 계획을 분석합니다. 전력, 용수, 인재 등 필수 인프라 구축의 현실적 과제를 짚어보고, 최근 시장의 화두인 AI 반도체의 '칩플레이션' 현상과 조정 국면에 대한 전문가들의 심도 있는 경제 토크를 제공합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 대규모 투자 발표 이면의 실질적인 인프라 구축 난관과 AI 반도체 시장의 조정 가능성을 균형 있게 파악하는 것이 중요합니다.</t>
   </si>
   <si>
     <t>[지식뉴스] "AI 데이터센터, 이제 한국으로 몰려온다'"..빅테크가 앞다퉈 한국을 새 거점으로 점찍은 진짜 이유 (ft.조홍종 단국대 경제학과 교수) / 교양이를 부탁해</t>
@@ -125,10 +125,10 @@
     <t>24:20</t>
   </si>
   <si>
-    <t>본 영상은 AI 시대를 맞아 반도체만큼 중요해진 '전력'의 가치를 조명합니다. 미국 중심의 에너지 패권 변화 속에서 데이터센터와 제조업에 필수적인 전력 수급 문제와 한국의 전력 인프라 경쟁력을 분석합니다. 한국이 원전 및 전력기기 산업을 통해 글로벌 전력 시장에서 기회를 선점하고, 이를 통해 국가적 생존 전략을 어떻게 모색해야 하는지를 심도 있게 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️ AI 시대의 핵심은 반도체만이 아닌 전력망임을 이해해야 향후 글로벌 산업 지형과 투자 기회를 정확히 파악할 수 있습니다.</t>
+    <t>본 영상은 AI 시대의 핵심 자원으로 부상한 '전력'의 중요성을 다룹니다. 반도체 기술을 넘어 전력망 확보가 국가 경쟁력을 결정짓는 상황에서, 한국의 전력 인프라와 원전 기술이 어떻게 글로벌 시장에서 새로운 기회를 맞이하고 있는지 조홍종 교수의 분석을 통해 설명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 에너지 패권 전쟁이 단순한 유가 문제를 넘어 전기 인프라와 빅테크 기업의 전략적 선택으로 변모하고 있음을 이해하는 것이 중요합니다.</t>
   </si>
   <si>
     <t>재테크</t>
@@ -146,10 +146,10 @@
     <t>1:28:28</t>
   </si>
   <si>
-    <t>본 영상은 김진 앵커가 출연하여 한국 부동산 시장의 변화와 향후 집값 전망을 분석하는 내용을 담고 있습니다. 아파트 시장의 대대적인 변화가 예고된 2027년을 기점으로 주거 환경과 가격 변동성이 커질 것으로 예측하며, 부동산 시장의 흐름과 자산 가치 변화에 따른 대응 전략을 심도 있게 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 제목을 사용한 클릭베이트 요소가 있으므로, 특정 종목이나 정책에 대한 맹신보다는 거시적인 경제 흐름과 시장의 논리를 냉정하게 판단해야 합니다.</t>
+    <t>본 영상은 김진 앵커가 출연하여 한국 부동산 시장의 변화를 예고하며, 특히 2027년 이후 아파트 시장의 대대적인 구조적 변동을 강조합니다. 아파트 물갈이와 같은 정책적·시장적 환경 변화가 집값에 미칠 영향과 현금 자산의 운용 전략, 그리고 시장 침체기 속에서 주목해야 할 투자 자산에 대해 심도 있는 인사이트를 제공합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 문구를 사용하고 있으므로, 특정 정보에 의존하기보다 부동산 정책의 실질적인 변화와 경제 지표를 스스로 교차 검증하는 태도가 필요합니다.</t>
   </si>
   <si>
     <t>국민연금이 팔기 시작했다, 이거 모르면 큰일 난다</t>
@@ -164,10 +164,10 @@
     <t>9:53</t>
   </si>
   <si>
-    <t>재테크읽어주는 파일럿 채널에서 발행하는 미국 주식 비법서 출간 소식과 예약 구매 혜택을 알리는 영상입니다. 7월 8일부터 발송되는 신간의 내용과 더불어, 2권 세트 구매 시 대한항공 퍼스트클래스 왕복 항공권 이벤트에 자동 응모되는 내용을 포함하고 있습니다. 구독자들의 투자 성과를 돕기 위한 책임을 강조하며, 관심 있는 이들에게 예약 구매를 독려하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 투자 도서 홍보 영상이므로 실질적인 시장 분석보다 판매 정보 위주임을 인지하고 구매를 결정해야 합니다.</t>
+    <t>본 영상은 재테크 유튜버 '재테크 읽어주는 파일럿'의 신간 도서 출시 및 이벤트 홍보를 담고 있습니다. 미국 주식 투자 비법이 담긴 책을 소개하며, 예약 구매자 대상의 퍼스트클래스 항공권 증정 이벤트를 통해 시청자의 참여를 유도하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목과 같이 자극적인 내용을 내세워 신간 홍보 및 구매를 유도하는 영상이므로 실제 투자 정보보다는 마케팅 목적이 강함을 인지하고 시청해야 합니다.</t>
   </si>
   <si>
     <t>부동산 추가 규제 나왔다, 앞으로 집값 이렇게 됩니다</t>
@@ -179,10 +179,10 @@
     <t>21:18</t>
   </si>
   <si>
-    <t>본 영상은 정부의 기습적인 부동산 추가 규제 발표에 따른 시장 영향과 향후 집값 전망을 분석합니다. 새로운 규제가 즉시 시행됨에 따라 시장의 불확실성이 커진 상황에서, 실거주자 및 투자자가 정책 변화를 어떻게 해석하고 자산 가치를 지켜야 할지에 대한 대응 전략을 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️부동산 규제는 시장 흐름을 즉각적으로 변화시키므로, 발표 직후 정책의 세부 조항을 확인하고 실거주 목적인지 투자 목적인지에 따른 맞춤형 포트폴리오 재점검이 필수입니다.</t>
+    <t>본 영상은 정부의 기습적인 부동산 추가 규제 발표에 따른 시장 영향과 향후 집값 전망을 분석하는 내용을 다룹니다. 규제 시행 직후 적용되는 핵심 변경 사항들을 상세히 설명하며, 실수요자와 투자자가 현재 부동산 시장의 변화를 어떻게 이해하고 대응해야 할지에 대한 통찰을 제공합니다.</t>
+  </si>
+  <si>
+    <t>⚠️부동산 규제는 기습적으로 발표되는 경우가 많으므로 항상 최신 정부 공고를 확인하고 유연한 대응 전략을 수립해야 합니다.</t>
   </si>
   <si>
     <t>자기계발</t>
@@ -197,10 +197,10 @@
     <t>19:31</t>
   </si>
   <si>
-    <t>유튜버 정일영이 개그맨 허경환을 만나 프랑스 여행 계획을 세우며 인생 고민을 나누는 영상입니다. 허경환은 외국어 공부를 계속 미루는 자신의 고민을 털어놓고, 정일영은 이에 대한 조언과 함께 예능 선배로서의 노하우를 전수합니다. 두 사람의 진솔한 대화와 훈훈한 케미를 담고 있으며, 다음 편에는 황치열이 출연할 것을 예고하며 기대감을 높였습니다.</t>
-  </si>
-  <si>
-    <t>외국어 공부를 계속 미루고 있다면 정일영이 제시하는 프랑스어 박사만의 구체적인 학습 전략을 참고해 보세요.</t>
+    <t>유튜버 정일영이 개그맨 허경환을 만나 프랑스 여행 계획을 세우며 인생 고민을 나누는 영상입니다. 허경환은 외국어 공부를 미루는 고민을 털어놓고, 정일영은 이에 대한 학습 꿀팁과 연예계 활동에 대한 조언을 주고받습니다. 유쾌한 대화 속에서 두 사람의 진솔한 케미스트리를 엿볼 수 있습니다.</t>
+  </si>
+  <si>
+    <t>외국어 공부를 계속 미루고 있다면, 정일영이 제시하는 구체적인 학습 노하우를 통해 실천 가능한 작은 습관부터 시작해 보세요.</t>
   </si>
   <si>
     <t>헬스터디 이채연이 알려주는 국어 공부법</t>
@@ -215,397 +215,397 @@
     <t>15:40</t>
   </si>
   <si>
-    <t>헬스터디 출연자 이채연이 수험생들을 위해 자신의 국어 공부법을 공유하는 영상입니다. 기초적인 학습 방향성을 제시하며, 시청자들의 궁금증을 해결하기 위해 곧 2탄 영상을 올릴 것임을 예고했습니다. 수능 국어 성적 향상을 고민하는 학생들에게 실질적인 가이드를 제공합니다.</t>
-  </si>
-  <si>
-    <t>구체적인 공부 방법론은 곧 업로드될 2탄 영상을 통해 더욱 상세히 확인할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>잘되는 아이들 주변에는 꼭 ‘이런 어른’들이 있습니다 ㅣ Ep. 사람산책 14 (최재천 교수님 1부)</t>
-  </si>
-  <si>
-    <t>책과삶</t>
+    <t>헬스터디 출연자 이채연이 수험생들을 위해 자신만의 국어 공부법을 공유하는 영상입니다. 기초적인 학습 원리와 체계적인 접근 방식을 다루고 있으며, 수능 국어 영역에서 성적을 올리기 위한 실질적인 노하우를 제공합니다. 영상 말미에는 다음 주말에 업로드될 2탄을 예고하며 시청자와의 소통을 강조했습니다.</t>
+  </si>
+  <si>
+    <t>국어 영역의 근본적인 독해력 향상을 위해 이채연이 강조하는 체계적인 학습 루틴을 2탄과 함께 꾸준히 따라 해 보세요.</t>
+  </si>
+  <si>
+    <t>인생이 팍팍할 때 딱 1도만 바꿔보세요, 허리케인급 변화가 옵니다.</t>
+  </si>
+  <si>
+    <t>하와이 대저택</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>30:07</t>
+  </si>
+  <si>
+    <t>하와이 대저택 채널의 이 영상은 발타자르 그라시안과 세네카의 지혜를 빌려 인생의 고난을 극복하는 법을 다룹니다. 삶이 힘들 때 사소한 관점이나 태도를 1도만 바꾸어도 큰 변화를 끌어낼 수 있음을 강조하며, 잠재의식과 자아실현을 통해 더 나은 삶으로 도약하는 구체적인 실천 전략을 제시합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 거창한 계획보다 지금 당장 사고의 방향을 1도만 수정하는 것이 삶의 거대한 전환점을 만드는 핵심입니다.</t>
+  </si>
+  <si>
+    <t>게임</t>
+  </si>
+  <si>
+    <t>혜안져스 "메차 카멜레온" 이제 쥰내 잘합니다ㅋㅋㅋㅋㅋㅋ🔥</t>
+  </si>
+  <si>
+    <t>혜안</t>
+  </si>
+  <si>
+    <t>29:49</t>
+  </si>
+  <si>
+    <t>유튜버 혜안이 인기 콘텐츠 '숨꼭져스2' 시리즈의 일환으로 게임 내 '메챠 카멜레온' 플레이 실력이 비약적으로 상승했음을 보여주는 영상입니다. 멤버들과 함께 게임을 즐기며 성장한 실력을 유쾌하게 뽐내고, 특유의 예능감 넘치는 편집과 브금대통령의 배경음악이 더해져 시청자들에게 큰 웃음을 선사합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 클릭베이트성 제목을 활용하여 실력 향상을 강조했으나, 실제로는 예능적 재미를 추구하는 콘텐츠이므로 가벼운 마음으로 시청하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>저는 저를 숨겼습니다</t>
+  </si>
+  <si>
+    <t>랄로</t>
+  </si>
+  <si>
+    <t>47:24</t>
+  </si>
+  <si>
+    <t>유튜버 랄로가 자신의 과거와 솔직한 내면을 고백하는 영상입니다. 그동안 대중에게 보였던 이미지와 실제 자신의 모습 사이에서 느꼈던 괴리감, 그리고 자신을 숨겨야만 했던 심리적 배경을 진솔하게 풀어내며 시청자들과 정서적인 공감대를 형성하고 인간적인 고민을 공유합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 달리 개인적인 회고와 성찰을 담은 영상이므로, 랄로의 서사에 관심이 많은 시청자에게 추천합니다.</t>
+  </si>
+  <si>
+    <t>역전극 [T1scord 2026 vs GEN]</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>20:48</t>
+  </si>
+  <si>
+    <t>본 영상은 T1의 주요 선수들이 참여한 2026 시즌 T1scord(T1 디스코드)와 젠지(GEN) 간의 긴장감 넘치는 역전극 매치를 담고 있습니다. 경기 하이라이트를 통해 선수들의 개인 기량과 팀워크를 확인할 수 있으며, 다음 콘텐츠로 TLAW 및 KC전 업로드가 예고되어 팬들의 기대를 모으고 있습니다.</t>
+  </si>
+  <si>
+    <t>선수들의 개인 방송 채널 링크가 설명란에 기재되어 있으니, 생생한 실시간 반응을 확인하고 싶다면 각 채널을 방문해 보세요.</t>
+  </si>
+  <si>
+    <t>IT·테크</t>
+  </si>
+  <si>
+    <t>긴급속보 | 애플, 최소 20만원 넘게 가격 올려버렸다? 갑자기 이런 미친 결정을 한 진짜 이유</t>
+  </si>
+  <si>
+    <t>ITSub잇섭</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>12:18</t>
+  </si>
+  <si>
+    <t>애플이 2026년 6월 25일을 기점으로 주요 제품 라인업의 가격을 최소 5.7%에서 최대 54.3%까지 기습 인상했습니다. 잇섭은 메모리 부족 사태를 원인으로 분석하며, 이번 대규모 가격 인상 배경과 최근 한국 시장을 방문하는 글로벌 CEO들의 행보, 그리고 소비자들에게 미칠 영향에 대해 심도 있게 다루었습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 갑작스러운 가격 인상 정보는 소비심리를 자극하는 클릭베이트일 수 있으므로 반드시 공식 홈페이지의 실제 판매가를 확인해야 합니다.</t>
+  </si>
+  <si>
+    <t>플레이스토어가 나를 감시한다고? 갤럭시폰에서  ‘이 버튼’ 당장 끄고 개인정보와 스마트폰 배터리 둘 다 잡으세요!</t>
+  </si>
+  <si>
+    <t>시니어정보 양쌤</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>본 영상은 갤럭시 스마트폰 사용자를 대상으로 배터리 소모를 줄이고 개인정보를 보호하는 필수 설정법을 안내합니다. 구글 플레이스토어의 데이터 전송 차단, 위치 정보 및 진단 데이터 전송 해제, 안드로이드 맞춤형 서비스 중단 등 실제 화면을 통해 누구나 쉽게 따라 할 수 있는 최적화 과정을 상세히 설명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목은 다소 자극적이지만, 설명하는 설정들은 실제 스마트폰의 배터리 효율을 높이고 개인정보 유출을 방지하는 실용적인 최적화 방법입니다.</t>
+  </si>
+  <si>
+    <t>요즘 13만원짜리 게임기 RG 로테이트 수준</t>
+  </si>
+  <si>
+    <t>UNDERkg</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>안드로이드 기반의 휴대용 게임기 RG 로테이트에 대한 리뷰입니다. 약 87달러의 합리적인 가격에 화면이 90도 회전하며 게임패드가 나타나는 독특한 구조를 가졌습니다. 인터페이스와 조작감이 준수하며, 조작 버튼의 예비 부품을 제공하는 점이 인상적입니다. 다만 진동 모터의 위치 문제와 실제로는 없는 조도 센서에 대한 오해 등 일부 단점도 존재하지만, 전반적인 완성도는 가격 대비 매우 훌륭한 수준입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 가성비는 매우 좋지만 조작 버튼의 내구성 문제로 예비 부품을 제공하는 만큼, 버튼의 실제 사용감과 내구성을 충분히 고려하여 구매를 결정하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>라이프</t>
+  </si>
+  <si>
+    <t>일본 오사카에서 어깨빵하는 빌런 참교육 하는 육은영쌤</t>
+  </si>
+  <si>
+    <t>매드브로 MadBros</t>
+  </si>
+  <si>
+    <t>15:16</t>
+  </si>
+  <si>
+    <t>본 영상은 매드브로 채널의 육은영쌤이 일본 오사카 여행 중 무례하게 어깨를 치고 지나가는 현지인 빌런을 조우하여, 특유의 카리스마와 단호한 대처로 상황을 제압하고 참교육하는 모습을 담은 콘텐츠입니다. 공공장소에서의 비매너 행위에 굴하지 않고 당당하게 대응하는 과정을 통해 시청자들에게 통쾌함을 선사하며, 중간에 냉각 손선풍기 제품 홍보가 포함되어 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 유튜브 영상 제목에 포함된 '참교육'이나 '빌런' 등의 자극적인 키워드는 조회수를 유도하기 위한 클릭베이트 요소가 포함되어 있을 수 있습니다.</t>
+  </si>
+  <si>
+    <t>100시간 동안 세계에서 가장 오염된 도시에서 살면 생기는 일</t>
+  </si>
+  <si>
+    <t>고재영</t>
+  </si>
+  <si>
+    <t>45:14</t>
+  </si>
+  <si>
+    <t>유튜버 고재영이 세계에서 가장 오염된 도시로 알려진 지역을 직접 방문하여 100시간 동안 체류하며 겪는 생생한 체험기입니다. 현지의 열악한 환경과 대기 오염 수준을 몸소 체감하며, 해당 도시의 실제 생활 모습과 거주민들의 일상을 다큐멘터리 형식으로 솔직하게 담아냈습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목을 사용했으나, 실제 오염도의 심각성을 현장에서 직접 체험하며 보여주는 정보성 영상입니다.</t>
+  </si>
+  <si>
+    <t>아들이랑 둘이사는 서인영 절친 싱글맘 조민아 집 최초공개 (+오해와 진실)</t>
+  </si>
+  <si>
+    <t>개과천선 서인영</t>
+  </si>
+  <si>
+    <t>29:23</t>
+  </si>
+  <si>
+    <t>서인영이 절친 조민아의 집을 최초로 공개하며 과거 쌓였던 오해를 풀고 깊은 속마음을 나누는 시간을 가졌습니다. 쥬얼리 시절의 추억을 회상하며 서로의 진심을 확인하는 따뜻한 모습을 보여주었으며, 싱글맘인 조민아와 그녀의 아들 강호와의 다정한 일상을 조명했습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 갈등 해소를 주제로 내세웠으나 실제 내용은 출연진 간의 화해와 친목 도모를 강조하는 홍보성 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>【元テレ東×元朝日新聞対談】新聞とテレビは終わるのか？朝日毎日読売の生存戦略／ネット時代の「有料課金」は日経一人勝ちか？／AI時代求められるのは「誰が言っているか」【下矢一良×今野忍】｜選挙ドットコム</t>
+  </si>
+  <si>
+    <t>選挙ドットコムちゃんねる</t>
+  </si>
+  <si>
+    <t>1:03:15</t>
+  </si>
+  <si>
+    <t>전직 TV도쿄 디렉터 하타야 카즈요시와 아사히신문 정치부 기자 콘노 시노부가 출연하여 미디어의 생존 전략을 논합니다. 신문과 TV의 쇠퇴 속에서 니혼게이자이신문의 유료화 성공 요인을 분석하고, AI 시대에 정보의 신뢰성과 '발신자가 누구인가'라는 브랜드 가치가 왜 중요한지 깊이 있게 다룹니다.</t>
+  </si>
+  <si>
+    <t>AI 시대에는 정보의 홍수 속에서 매체와 기자의 신뢰성이 정보의 가치를 결정하는 핵심 요소가 된다는 점을 이해하면 좋습니다.</t>
+  </si>
+  <si>
+    <t>また韓国市場の暴落がAI関連へ波及！米軍がイランに対し空爆を実施！【6/27 米国株ニュース】</t>
+  </si>
+  <si>
+    <t>とも米国株投資チャンネル</t>
+  </si>
+  <si>
+    <t>15:19</t>
+  </si>
+  <si>
+    <t>본 영상은 한국 시장의 급락세가 AI 관련 주식으로 확산되는 현상과 미군의 이란 공습 소식을 다룹니다. 글로벌 지정학적 리스크와 특정 시장의 하락이 미국 증시에 미치는 영향력을 분석하며, 투자자들이 유의해야 할 시장 변동성과 자산 배분의 중요성을 강조하는 미국 주식 투자 뉴스입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 달리 실제 내용은 경제 뉴스 요약 중심이므로 정보를 객관적으로 필터링하여 투자 판단에 활용하시기 바랍니다.</t>
+  </si>
+  <si>
+    <t>資産1000万円超えると人生が激変する理由</t>
+  </si>
+  <si>
+    <t>高須幹弥（高須クリニック）</t>
+  </si>
+  <si>
+    <t>20:31</t>
+  </si>
+  <si>
+    <t>타카스 미키야 원장은 자산 1,000만 엔을 넘기는 것이 인생의 중요한 전환점이라고 강조합니다. 이 금액을 달성하면 심리적 여유와 선택의 폭이 넓어지며, 사회적 신용과 투자 기회도 확대되어 자산 증식 속도가 붙는 선순환 구조가 형성된다고 설명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자산 1,000만 엔은 단순히 돈의 액수를 넘어 경제적 자유와 기회를 잡기 위한 최소한의 발판이자 심리적 안정장치라는 점을 명심하세요.</t>
+  </si>
+  <si>
+    <t>【元手200万→10億円】キオクシアだけを見るな！次の注目はTOPIX？／新NISA「最初の3000万円」がカギ／億を目指す4つの投資方法《上岡正明》</t>
+  </si>
+  <si>
+    <t>楽待 RAKUMACHI</t>
+  </si>
+  <si>
+    <t>53:57</t>
+  </si>
+  <si>
+    <t>자산 200만 엔으로 시작해 10억 엔을 달성한 투자자 카미오카 마사아키가 자산 증식의 핵심 전략을 전합니다. 특히 자산 3,000만 엔 구간의 중요성과 신NISA 활용법, 폭락장 대응 전략, 그리고 핵심 자산과 주변 자산을 배분하는 포트폴리오 운용법을 통해 부를 쌓는 실질적인 투자 노하우를 상세히 설명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자산 3,000만 엔까지는 복리 효과가 미미하므로 철저한 저축과 공격적 투자를 병행하여 이 임계점을 빠르게 넘기는 것이 자산 형성의 핵심입니다.</t>
+  </si>
+  <si>
+    <t>退職後に2億円全力投資、お金が減るとこうなる【資産公開】</t>
+  </si>
+  <si>
+    <t>S&amp;P500最強伝説</t>
+  </si>
+  <si>
+    <t>37:52</t>
+  </si>
+  <si>
+    <t>은퇴 후 2억 엔이라는 거액을 투자 시장에 올인한 투자자의 실제 자산 변동 사례를 분석한 영상입니다. 시장 변동성에 따라 자산이 감소하는 상황에서 느끼는 심리적 불안감과 이를 극복하기 위한 투자자의 자세를 공유하며, 노후 자산 관리의 현실적인 측면을 다루고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 거액을 투자할 때는 시장의 단기적인 하락에 일희일비하지 않도록 자신의 투자 철학과 현금 흐름을 미리 철저히 점검해야 합니다.</t>
+  </si>
+  <si>
+    <t>【全紹介】1〜100までの全素数の倍数判定法あなたは知っていますか？</t>
+  </si>
+  <si>
+    <t>日常でんがん</t>
+  </si>
+  <si>
+    <t>10:18</t>
+  </si>
+  <si>
+    <t>본 영상은 유튜브 채널 '일상 뎅간'의 운영자 뎅간이 출연하여 자신의 채널을 소개하고 교육 콘텐츠의 방향성을 설명하는 영상입니다. 과거 '하나오 뎅간' 활동을 거쳐 현재는 혼자서 공부법이나 수학 해설 등 지식 기반 콘텐츠를 제작하고 있음을 밝히며, 본인이 집필한 공부법 도서 '바보를 위한 공부 100조'를 홍보하고 구독자들에게 꾸준한 시청과 응원을 부탁하는 내용으로 구성되어 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 제목은 소수의 배수 판정법을 다룰 것처럼 자극적으로 작성되었으나, 실제 내용은 채널 소개와 저서 홍보에 집중된 점을 유의하여 시청하십시오.</t>
+  </si>
+  <si>
+    <t>院生vlog🫙勉強無し生活に困惑 | 社会人になる準備 | パース, ロットネスト島旅🚢 《オーストラリア》</t>
+  </si>
+  <si>
+    <t>Okisvlog</t>
+  </si>
+  <si>
+    <t>27:37</t>
+  </si>
+  <si>
+    <t>대학 졸업 후 사회인 입사 전, 호주에서 보내는 공백기 일상을 담은 브이로그입니다. 학업 없이 한가해진 시간을 활용해 요리와 베이킹, 컬러링 등을 하며 재충전하는 모습과 퍼스 및 로트네스트 섬 여행기를 기록했습니다. 곧 닥쳐올 일본 귀국과 입사 준비 전, 온전히 나만의 시간을 즐기며 마음을 다잡는 여유로운 일상을 공유합니다.</t>
+  </si>
+  <si>
+    <t>입사 전 불안감이 들 때는 거창한 계획보다 평소 미뤄두었던 취미나 정적인 활동을 통해 온전한 휴식을 취하는 것이 큰 도움이 됩니다.</t>
+  </si>
+  <si>
+    <t>【受験の天王山が始まる...】前に必ず見てほしい高3向け"7月の勉強法"を解説します。</t>
+  </si>
+  <si>
+    <t>河野塾チャンネル</t>
+  </si>
+  <si>
+    <t>6:16</t>
+  </si>
+  <si>
+    <t>본 영상은 입시의 승부처인 7월을 앞둔 고3 수험생을 위해 고노 겐토가 이끄는 고노 학원의 공부 전략을 다룹니다. 여름방학 전후 시기의 중요성을 강조하며, 성적 향상을 위한 효과적인 학습 계획 수립과 기초 완성의 필요성을 역설합니다. 아울러 무료 모의고사 참여 및 특별 강좌 캠페인 정보를 통해 수험생들의 실전 감각 배양과 취약점 보완을 돕는 구체적인 학습 가이드를 제시합니다.</t>
+  </si>
+  <si>
+    <t>⚠️입시의 성패를 가르는 7월, 단순히 양을 늘리기보다 기초를 철저히 점검하고 보완하는 전략적 학습이 수능 성공의 열쇠입니다.</t>
+  </si>
+  <si>
+    <t>음악</t>
+  </si>
+  <si>
+    <t>「瞬間ジャーニー」 Music Video ／ TOP4(キヨ・レトルト・牛沢・ガッチマン)</t>
+  </si>
+  <si>
+    <t>キヨ。</t>
+  </si>
+  <si>
+    <t>3:49</t>
+  </si>
+  <si>
+    <t>유명 게임 실황자 그룹 TOP4(키요, 레토르트, 우시자와, 갓치만)가 발표한 오리지널 곡 '순간 저니'의 뮤직비디오입니다. ORANGE RANGE의 HIROKI와 NAOTO가 각각 작사와 작곡을 맡아 화제가 되었으며, 멤버들의 개성을 담은 모션 그래픽이 돋보이는 영상입니다. 6월 27일부터 주요 스트리밍 서비스를 통해 음원이 공개되었습니다.</t>
+  </si>
+  <si>
+    <t>영상 설명란의 링크를 통해 주요 음원 사이트에서 정식 음원을 감상할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>IS:SUE (イッシュ) 'come again' (Original by m-flo) Live Performance [2026.06.19 REBORN Collection 2026]</t>
+  </si>
+  <si>
+    <t>IS:SUE</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>5:04</t>
+  </si>
+  <si>
+    <t>본 영상은 걸그룹 IS:SUE가 2026년 6월 19일 'REBORN Collection 2026' 행사에서 m-flo의 히트곡 'come again'을 자신들만의 색깔로 재해석한 라이브 공연 영상입니다. 세련된 퍼포먼스와 보컬 실력을 통해 멤버들의 뛰어난 무대 장악력을 확인할 수 있으며, 이들의 최신 앨범 'QUARTET' 활동과 다가오는 두 번째 투어 소식도 함께 확인할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>영상 하단 설명란에 링크된 IS:SUE의 댄스 연습 영상과 1집 앨범 정보를 확인하면 이들의 음악적 색깔을 더 깊이 이해할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>1人で新作リズム天国を先行プレイして俺より壊れてる奴いんの？</t>
+  </si>
+  <si>
+    <t>1:40:35</t>
+  </si>
+  <si>
+    <t>유명 게임 유튜버 키요가 닌텐도 스위치 신작 '리듬세상 미라클 스타즈'를 사전 플레이하며 특유의 텐션으로 리듬 게임을 즐기는 영상입니다. 공식 협업을 통해 제작된 콘텐츠로, 게임의 재미와 키요의 익살스러운 반응이 조화를 이루며 리듬 게임 특유의 몰입감과 코믹함을 동시에 보여줍니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목은 유튜버 특유의 예능적 과장이며 실제로는 공식 협업을 통한 유쾌한 게임 플레이 영상입니다.</t>
+  </si>
+  <si>
+    <t>【マインクラフト】地下の強制労働施設で埋蔵金を探すことになりました【日常組】</t>
+  </si>
+  <si>
+    <t>日常組</t>
+  </si>
+  <si>
+    <t>1:34:58</t>
+  </si>
+  <si>
+    <t>일상조(日常組) 멤버들이 마인크래프트 내의 지하 강제 노동 시설에서 매장금을 찾아 탈출하는 모험을 담은 영상입니다. 특유의 유쾌한 입담과 상황극을 통해 노동 시설이라는 독특한 맵을 탐험하며 보물을 찾는 과정에서 발생하는 멤버들 간의 케미스트리와 코믹한 돌발 상황들이 주된 재미 요소입니다.</t>
+  </si>
+  <si>
+    <t>일상조 특유의 상황극을 즐기는 팬이라면 멤버들의 티키타카를 중심으로 시청하면 더욱 재미있습니다.</t>
+  </si>
+  <si>
+    <t>【4人】「全員一致ゲーム＆全員不一致ゲーム」で連続目指したら地獄でした</t>
+  </si>
+  <si>
+    <t>レトルト</t>
+  </si>
+  <si>
+    <t>52:53</t>
+  </si>
+  <si>
+    <t>인기 게임 실황자 4인방(레토르트, 키요, 우시자와, 갓치만)이 '전원 일치 게임'과 '전원 불일치 게임'에 도전하며 벌어지는 소동을 담았습니다. 원래 공개되지 못했던 편집본을 모아 제작된 영상으로, 네 사람의 환상적인 케미와 엇갈리는 호흡이 큰 웃음을 자아냅니다. 긴박한 상황 속에서도 계속되는 실패가 오히려 유쾌한 재미를 선사하는 실황 예능입니다.</t>
+  </si>
+  <si>
+    <t>일본 실황계의 베테랑 4인방이 펼치는 입담과 예능감 덕분에 일본 게임 실황 문화를 이해하기에 매우 좋은 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>【今すぐオフ】Googleアカウントの新しいプライバシー設定と3つの変更点をわかりやすく解説！【2026年6月～】</t>
+  </si>
+  <si>
+    <t>スマホのコンシェルジュ「株式会社コアコンシェル」</t>
   </si>
   <si>
     <t>2026-06-27</t>
   </si>
   <si>
-    <t>26:48</t>
-  </si>
-  <si>
-    <t>최재천 교수가 출연하여 '선한 야망'을 주제로 삶의 태도와 교육관을 논합니다. 능력주의 사회의 위험성을 경고하고, 나이 듦에 따른 품격, 좋아하는 일의 가치, 그리고 자녀를 성장시키는 부모의 역할에 대해 통찰력 있는 조언을 건넵니다.</t>
-  </si>
-  <si>
-    <t>자녀를 성공으로 이끌고 싶다면 성취를 강요하기보다 스스로 좋아하는 일을 찾고 몰입할 수 있도록 돕는 어른이 되어야 합니다.</t>
-  </si>
-  <si>
-    <t>게임</t>
-  </si>
-  <si>
-    <t>혜안져스 "메차 카멜레온" 이제 쥰내 잘합니다ㅋㅋㅋㅋㅋㅋ🔥</t>
-  </si>
-  <si>
-    <t>혜안</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>29:49</t>
-  </si>
-  <si>
-    <t>유튜버 혜안이 멤버들과 함께 '메타 카멜레온' 게임을 플레이하며 펼치는 유쾌한 상황을 담은 영상입니다. 초반에는 서툴렀던 실력이 점차 향상되어 능숙하게 게임을 즐기는 과정을 보여주며, 특유의 티키타카와 재치 있는 입담을 통해 시청자들에게 큰 웃음을 선사합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 클릭베이트성 제목을 활용한 예능형 콘텐츠이므로, 게임 실력 그 자체보다는 출연진 간의 재미있는 상황극과 리액션을 위주로 감상하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>저는 저를 숨겼습니다</t>
-  </si>
-  <si>
-    <t>랄로</t>
-  </si>
-  <si>
-    <t>47:24</t>
-  </si>
-  <si>
-    <t>유튜버 랄로가 자신의 과거와 솔직한 내면을 고백하는 영상입니다. 그동안 대중 앞에 자신의 진짜 모습을 숨기고 가식적으로 행동해왔던 점을 인정하며, 시청자들에게 느끼는 부채감과 앞으로 진정성 있는 태도로 소통하고 싶다는 개인적인 다짐을 담담하게 이야기합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 썸네일과 달리 실제 영상은 인간적인 고뇌와 진솔한 심경 고백이 중심이 되는 콘텐츠입니다.</t>
-  </si>
-  <si>
-    <t>역전극 [T1scord 2026 vs GEN]</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>20:48</t>
-  </si>
-  <si>
-    <t>T1의 공식 유튜브 채널에 업로드된 영상으로, T1 선수들과 젠지(GEN) 간의 긴장감 넘치는 경기 내용을 다룬 역전극 콘텐츠입니다. 선수들의 경기력과 팀워크를 엿볼 수 있으며, 다음 일정으로 TLAW 및 KC전 업로드 소식을 함께 전하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ T1 선수들의 생생한 개인 방송을 시청하고 싶다면 설명란에 기재된 공식 숲(SOOP) 방송국 링크를 통해 확인해 보세요.</t>
-  </si>
-  <si>
-    <t>IT·테크</t>
-  </si>
-  <si>
-    <t>긴급속보 | 애플, 최소 20만원 넘게 가격 올려버렸다? 갑자기 이런 미친 결정을 한 진짜 이유</t>
-  </si>
-  <si>
-    <t>ITSub잇섭</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>12:18</t>
-  </si>
-  <si>
-    <t>애플이 2026년 6월 25일부로 대부분의 제품군 가격을 최소 5.7%에서 최대 54.3%까지 기습 인상했습니다. 잇섭은 이번 인상의 배경으로 최근 지속되는 글로벌 메모리 부족 사태를 지목하며, 제품별 구체적인 인상 폭과 함께 한국 시장의 위상 및 애플의 가격 정책 변화에 대해 심도 있게 분석했습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 갑작스러운 대규모 가격 인상은 글로벌 부품 수급 상황과 밀접한 연관이 있으므로, 애플 제품 구매 전 해당 시점의 부품 단가 변동 이슈를 미리 확인하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>플레이스토어가 나를 감시한다고? 갤럭시폰에서  ‘이 버튼’ 당장 끄고 개인정보와 스마트폰 배터리 둘 다 잡으세요!</t>
-  </si>
-  <si>
-    <t>시니어정보 양쌤</t>
-  </si>
-  <si>
-    <t>2026-06-06</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>본 영상은 갤럭시 스마트폰 사용자가 배터리 소모를 줄이고 개인정보를 보호할 수 있는 필수 설정법을 안내합니다. 구글 플레이스토어의 데이터 수집 차단, 위치 정보 및 진단 데이터 전송 해제, 안드로이드 맞춤형 서비스 중단 등 실제 화면을 보며 따라 할 수 있는 최적화 과정을 상세히 다루어 스마트폰 성능 향상과 보안 강화를 돕습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 불필요한 데이터 전송 설정을 끄는 것만으로도 스마트폰의 발열을 줄이고 배터리 수명을 효과적으로 연장할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>요즘 13만원짜리 게임기 RG 로테이트 수준</t>
-  </si>
-  <si>
-    <t>UNDERkg</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>UNDERkg이 리뷰한 13만 원대 안드로이드 게임기 RG 로테이트는 화면이 90도 회전하며 게임패드가 나타나는 독특한 구조가 특징입니다. 합리적인 가격대와 준수한 인터페이스, 조작감을 갖췄으나 L2/R2 버튼의 조작성과 진동 모터 위치, 조도 센서 부재 등 몇 가지 아쉬운 마감이 존재합니다.</t>
-  </si>
-  <si>
-    <t>저렴한 가격에 독특한 폼팩터를 경험할 수 있지만, L2/R2 버튼의 불편함과 기능적 마감 부족을 미리 인지하고 구매를 결정하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>라이프</t>
-  </si>
-  <si>
-    <t>일본 오사카에서 어깨빵하는 빌런 참교육 하는 육은영쌤</t>
-  </si>
-  <si>
-    <t>매드브로 MadBros</t>
-  </si>
-  <si>
-    <t>15:16</t>
-  </si>
-  <si>
-    <t>본 영상은 유튜브 채널 '매드브로'의 콘텐츠로, 일본 오사카 여행 중 길거리에서 의도적으로 어깨를 부딪치며 위협을 가하는 이른바 '어깨빵 빌런'을 만난 육은영쌤이 이를 당당하게 대처하고 참교육하는 과정을 담고 있습니다. 영상은 여행지에서의 돌발 상황에 대한 긴장감과 이를 슬기롭게 해결하는 과정을 통해 시청자들에게 카타르시스를 제공하며, 중간에 냉각 손선풍기 광고가 포함되어 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 해당 영상은 갈등 상황을 연출하거나 자극적인 요소를 활용한 클릭베이트성 콘텐츠일 수 있으므로 재미 위주로 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>100시간 동안 세계에서 가장 오염된 도시에서 살면 생기는 일</t>
-  </si>
-  <si>
-    <t>고재영</t>
-  </si>
-  <si>
-    <t>45:14</t>
-  </si>
-  <si>
-    <t>유튜버 고재영이 세계에서 가장 공기가 나쁜 것으로 알려진 도시에서 100시간 동안 직접 거주하며 겪는 생존기와 현지의 대기 오염 실태를 다룬 영상입니다. 극심한 대기 오염 속에서 신체적 변화와 현지인들의 생활상을 관찰하며 환경 문제의 심각성을 생생하게 전달합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목과 썸네일은 시청자의 호기심을 유도하는 자극적인 요소를 포함하고 있으므로, 정보성보다는 체험형 예능 콘텐츠로 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>아들이랑 둘이사는 서인영 절친 싱글맘 조민아 집 최초공개 (+오해와 진실)</t>
-  </si>
-  <si>
-    <t>개과천선 서인영</t>
-  </si>
-  <si>
-    <t>29:23</t>
-  </si>
-  <si>
-    <t>서인영이 절친 조민아의 집을 방문하여 쥬얼리 시절 겪었던 과거의 오해를 풀고 진솔한 대화를 나누는 모습을 담았습니다. 아들과 함께 홀로 육아를 이어가는 조민아의 일상을 공개하며, 두 사람이 오랜만에 회포를 풀고 변치 않는 우정을 확인하는 따뜻한 시간을 보여줍니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 갈등 해소를 기대하기보다는 쥬얼리 멤버들의 과거 서사와 싱글맘 조민아의 근황을 확인하는 데 초점이 맞춰진 브이로그입니다.</t>
-  </si>
-  <si>
-    <t>일본</t>
-  </si>
-  <si>
-    <t>【元テレ東×元朝日新聞対談】新聞とテレビは終わるのか？朝日毎日読売の生存戦略／ネット時代の「有料課金」は日経一人勝ちか？／AI時代求められるのは「誰が言っているか」【下矢一良×今野忍】｜選挙ドットコム</t>
-  </si>
-  <si>
-    <t>選挙ドットコムちゃんねる</t>
-  </si>
-  <si>
-    <t>1:03:15</t>
-  </si>
-  <si>
-    <t>전직 TV도쿄 디렉터이자 PR 전문가인 시모야 카즈요시와 아사히신문 정치부 기자 콘노 시노부가 대담을 나눕니다. 급변하는 미디어 환경 속에서 신문과 방송의 생존 전략을 논하고, 닛케이신문의 유료화 성공 사례와 AI 시대에 필요한 신뢰성 있는 정보의 중요성을 심층적으로 분석합니다.</t>
-  </si>
-  <si>
-    <t>전통 언론 매체가 디지털 전환 시대에 어떻게 영향력을 유지하고 유료 비즈니스 모델을 구축해야 하는지에 대한 업계 전문가의 시각을 확인할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>また韓国市場の暴落がAI関連へ波及！米軍がイランに対し空爆を実施！【6/27 米国株ニュース】</t>
-  </si>
-  <si>
-    <t>とも米国株投資チャンネル</t>
-  </si>
-  <si>
-    <t>15:19</t>
-  </si>
-  <si>
-    <t>본 영상은 한국 증시의 급락세가 AI 관련주로 확산하는 현상과 미군의 이란 공습 소식을 다룹니다. 글로벌 지정학적 리스크와 특정 시장의 하락이 미국 증시에 미치는 잠재적 영향력을 분석하며, 투자자들에게 시장 변동성에 대비한 리스크 관리의 중요성을 강조하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목에 자극적인 이슈를 언급하여 클릭을 유도하고 있으므로, 실제 뉴스 원문을 교차 확인하여 투자 결정 시 감정적 대응을 자제해야 합니다.</t>
-  </si>
-  <si>
-    <t>資産1000万円超えると人生が激変する理由</t>
-  </si>
-  <si>
-    <t>高須幹弥（高須クリニック）</t>
-  </si>
-  <si>
-    <t>20:31</t>
-  </si>
-  <si>
-    <t>다카스 미키야 원장이 자산 1,000만 엔을 넘기는 순간 삶이 어떻게 변화하는지 설명합니다. 심리적 여유가 생기며 선택의 폭이 넓어지고, 자본주의 사회에서 돈이 주는 심리적 안정감과 자신감이 인생을 긍정적인 방향으로 이끄는 원동력이 됨을 강조합니다.</t>
-  </si>
-  <si>
-    <t>⚠️자산 1,000만 엔은 단순한 숫자가 아니라 인생의 선택권을 넓히고 심리적 안정감을 확보하는 중요한 전환점입니다.</t>
-  </si>
-  <si>
-    <t>【元手200万→10億円】キオクシアだけを見るな！次の注目はTOPIX？／新NISA「最初の3000万円」がカギ／億を目指す4つの投資方法《上岡正明》</t>
-  </si>
-  <si>
-    <t>楽待 RAKUMACHI</t>
-  </si>
-  <si>
-    <t>53:57</t>
-  </si>
-  <si>
-    <t>본 영상은 자산 10억 엔을 달성한 투자자 카미오카 마사아키가 출연해 초기 자산 200만 엔에서 시작한 투자 철학을 공유합니다. 자산 3,000만 엔까지는 복리 효과가 크지 않아 공격적 투자가 필요하며, 신NISA 제도를 활용한 자산 배분 전략과 폭락장에 대비하는 투자자의 마음가짐 및 구체적인 핵심 자산 운용법을 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️자산 3,000만 엔 구간을 돌파하는 것이 투자의 임계점이며, 이를 넘어서야 복리 효과를 통한 자산 증식이 가속화됩니다.</t>
-  </si>
-  <si>
-    <t>退職後に2億円全力投資、お金が減るとこうなる【資産公開】</t>
-  </si>
-  <si>
-    <t>S&amp;P500最強伝説</t>
-  </si>
-  <si>
-    <t>37:52</t>
-  </si>
-  <si>
-    <t>은퇴 후 2억 엔이라는 거액의 자산을 S&amp;P500 중심의 투자 상품에 올인한 유튜버가 시장 변동성에 따른 자산 감소 과정을 솔직하게 공개하는 영상입니다. 고액 투자자가 겪는 심리적 압박과 자산 변동의 현실을 가감 없이 보여주며, 장기 투자 관점에서의 자산 운용 전략과 마인드셋을 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 거액을 한 번에 투자하는 전략은 시장 하락기 심리적 고통이 극심하므로 자신의 리스크 감당 능력을 객관적으로 파악하는 것이 우선입니다.</t>
-  </si>
-  <si>
-    <t>【全紹介】1〜100までの全素数の倍数判定法あなたは知っていますか？</t>
-  </si>
-  <si>
-    <t>日常でんがん</t>
-  </si>
-  <si>
-    <t>10:18</t>
-  </si>
-  <si>
-    <t>본 영상은 유튜버 뎅간이 운영하는 '일상 뎅간' 채널의 소개 영상입니다. 과거 '하나오뎅간' 채널을 운영했던 경험을 바탕으로, 현재는 혼자서 공부 방법론과 수학 해설 등 교육 콘텐츠를 중심으로 활동하고 있음을 밝힙니다. 또한 자신의 학습 경험을 담은 저서 '원래 바보였던 사람에 의한 바보를 위한 공부 100조'를 홍보하며, 시청자들과 소통하고 학습 동기를 부여하는 활동에 주력하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 학습 효율을 높이고 싶은 학생이라면 뎅간이 출간한 공부법 책을 통해 저자의 구체적인 학습 노하우를 참고해 보세요.</t>
-  </si>
-  <si>
-    <t>院生vlog🫙勉強無し生活に困惑 | 社会人になる準備 | パース, ロットネスト島旅🚢 《オーストラリア》</t>
-  </si>
-  <si>
-    <t>Okisvlog</t>
-  </si>
-  <si>
-    <t>27:37</t>
-  </si>
-  <si>
-    <t>대학원 졸업 후 사회인 입사 전, 호주 퍼스에서의 여유로운 일상을 담은 브이로그입니다. 쿼카가 있는 로트네스트 섬 여행과 요리, 베이킹, 컬러링 등을 하며 자신을 돌아보는 시간을 갖습니다. 일본 귀국 후 바쁜 이사 및 행정 절차를 앞두고 온전한 쉼을 즐기는 모습과 함께, 새로운 시작을 준비하는 차분한 마음가짐을 공유합니다.</t>
-  </si>
-  <si>
-    <t>사회인 입사 전의 막막한 공백기를 불안해하기보다, 자신만의 속도로 일상을 채우며 온전히 재충전하는 시간을 갖는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>【受験の天王山が始まる...】前に必ず見てほしい高3向け"7月の勉強法"を解説します。</t>
-  </si>
-  <si>
-    <t>河野塾チャンネル</t>
-  </si>
-  <si>
-    <t>6:16</t>
-  </si>
-  <si>
-    <t>본 영상은 입시의 승부처인 7월을 앞둔 고3 수험생을 위해 고노 겐토가 이끄는 고노 학원 강사진이 제안하는 효율적인 학습 전략을 다룹니다. 여름방학 전 기초를 확실히 다지고 공통 테스트 대비 모의고사를 적극 활용하여 자신의 약점을 파악하고 성적 향상을 이룰 수 있는 구체적인 학습 방향과 여름 캠페인 정보를 상세히 설명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 입시의 승부처인 7월에 자신의 객관적인 위치를 파악하고 취약점을 보완하는 것이 수험 생활의 성패를 가르는 핵심입니다.</t>
-  </si>
-  <si>
-    <t>음악</t>
-  </si>
-  <si>
-    <t>「瞬間ジャーニー」 Music Video ／ TOP4(キヨ・レトルト・牛沢・ガッチマン)</t>
-  </si>
-  <si>
-    <t>キヨ。</t>
-  </si>
-  <si>
-    <t>3:49</t>
-  </si>
-  <si>
-    <t>본 영상은 인기 게임 실황자 그룹 TOP4(키요, 레토르트, 우시자와, 갓치만)가 발표한 곡 '순간 저니(瞬間ジャーニー)'의 공식 뮤직비디오입니다. ORANGE RANGE의 HIROKI와 NAOTO가 각각 작사와 작곡을 맡아 화제를 모았으며, 4인의 유쾌한 매력과 청량한 분위기가 돋보이는 곡입니다.</t>
-  </si>
-  <si>
-    <t>6월 27일부터 주요 음악 스트리밍 플랫폼에서 정식 음원 감상이 가능합니다.</t>
-  </si>
-  <si>
-    <t>IS:SUE (イッシュ) 'come again' (Original by m-flo) Live Performance [2026.06.19 REBORN Collection 2026]</t>
-  </si>
-  <si>
-    <t>IS:SUE</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>5:04</t>
-  </si>
-  <si>
-    <t>본 영상은 걸그룹 IS:SUE(이슈)가 2026년 6월 19일 개최된 'REBORN Collection 2026' 무대에서 선보인 m-flo의 히트곡 'come again' 라이브 퍼포먼스 영상입니다. 세련된 퍼포먼스와 멤버들의 가창력이 돋보이며, 영상 설명란을 통해 정규 1집 'QUARTET' 정보 및 2번째 투어 개최 소식 등 그룹의 최신 활동 정보를 함께 확인할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>영상 설명란의 링크를 통해 IS:SUE의 1집 앨범 'QUARTET' 정보와 다가오는 2번째 투어 일정 등 공식 활동 소식을 미리 확인해 보세요.</t>
-  </si>
-  <si>
-    <t>1人で新作リズム天国を先行プレイして俺より壊れてる奴いんの？</t>
-  </si>
-  <si>
-    <t>1:40:35</t>
-  </si>
-  <si>
-    <t>유명 게임 실황자 키요(キヨ。)가 닌텐도의 신작 '리듬천국 미라클 스타즈'를 선행 플레이하는 영상입니다. 특유의 에너지 넘치는 진행과 함께 리듬 게임 특유의 박자감과 코믹한 리액션을 보여주며, 시청자들에게 게임의 재미와 분위기를 생생하게 전달합니다. 닌텐도의 공식 협력을 받아 제작되었으며, 게임의 독특한 리듬 메커니즘을 경험하며 즐거워하는 모습이 담겨 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 게임의 고난도 리듬 패턴을 플레이할 때 박자를 놓치지 않으려면 배경음악의 베이스 음을 듣는 것이 도움이 됩니다.</t>
-  </si>
-  <si>
-    <t>【マインクラフト】地下の強制労働施設で埋蔵金を探すことになりました【日常組】</t>
-  </si>
-  <si>
-    <t>日常組</t>
-  </si>
-  <si>
-    <t>1:34:58</t>
-  </si>
-  <si>
-    <t>일상조(日常組) 멤버 4명이 마인크래프트 내의 지하 강제 노동 시설에 갇혀 매장금을 찾아 탈출하기 위해 분투하는 게임 실황 영상입니다. 독특한 맵 환경 속에서 멤버 특유의 유머러스한 티키타카와 협동 과정을 통해 상황을 해결해 나가는 재미를 선사합니다.</t>
-  </si>
-  <si>
-    <t>일상조 멤버 간의 케미스트리와 만담이 주된 재미 요소이므로, 자막을 통해 대화의 흐름을 따라가면 더욱 즐겁게 시청할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>【4人】「全員一致ゲーム＆全員不一致ゲーム」で連続目指したら地獄でした</t>
-  </si>
-  <si>
-    <t>レトルト</t>
-  </si>
-  <si>
-    <t>52:53</t>
-  </si>
-  <si>
-    <t>인기 실황자 레토르트, 키요, 우시자와, 가치맨 4인이 모여 '전원 일치 게임'과 '전원 불일치 게임'에 도전하는 영상입니다. 연속 성공을 목표로 고군분투하지만, 서로의 의견이 엇갈리며 발생하는 엉뚱한 상황과 예기치 못한 실패 과정이 큰 웃음을 자아냅니다. 기존에 공개되지 않았던 미공개 영상을 모아 편집한 기획물로, 멤버들의 완벽하지 않은 호흡이 오히려 재미 포인트가 됩니다.</t>
-  </si>
-  <si>
-    <t>멤버 간의 독특한 사고방식 차이를 확인하며 즐기면 더욱 재미있게 시청할 수 있습니다.</t>
-  </si>
-  <si>
-    <t>【今すぐオフ】Googleアカウントの新しいプライバシー設定と3つの変更点をわかりやすく解説！【2026年6月～】</t>
-  </si>
-  <si>
-    <t>スマホのコンシェルジュ「株式会社コアコンシェル」</t>
-  </si>
-  <si>
     <t>9:20</t>
   </si>
   <si>
-    <t>Google이 발표한 새로운 개인정보 보호 정책 변경 사항을 다룹니다. 2026년 6월부터 적용되는 검색 서비스 기록과 미디어 저장 방식의 변화를 상세히 설명하며, 사용자가 데이터 관리와 개인화 설정을 스스로 제어할 수 있도록 돕는 구체적인 설정 변경 가이드를 제공합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 구글 계정의 데이터 수집과 개인화 설정을 유지하고 싶지 않다면 영상에서 안내하는 '미디어 저장' 및 '검색 서비스 기록' 설정을 지금 바로 확인하여 해제하십시오.</t>
+    <t>Google이 2026년 6월부터 적용하는 새로운 개인정보 보호 설정과 주요 변경 사항을 다룹니다. 특히 검색 서비스 이용 기록과 미디어 저장 설정이 핵심이며, 개인화된 맞춤 서비스 환경에서 사용자가 반드시 확인하고 수정해야 할 설정값과 그 필요성을 상세히 안내합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 구글 계정의 개인정보 보호 설정을 방치하면 검색 기록과 미디어 데이터가 무분별하게 수집될 수 있으니 지금 즉시 설정을 점검하고 불필요한 항목은 비활성화하세요.</t>
   </si>
   <si>
     <t>【ルームツアー?】自宅にクソでかサーバーを作ったYouTuberがいるらしいので調査してきました。</t>
@@ -617,10 +617,10 @@
     <t>25:48</t>
   </si>
   <si>
-    <t>IT 유튜버 TECH WORLD가 '운차마(うんちゃま)'의 자택을 방문하여 구축해 놓은 거대한 서버실을 소개하는 영상입니다. 일반 가정집에서는 보기 힘든 고성능 서버 환경과 인프라 구성을 상세히 보여주며, 개인 서버 운영에 관심 있는 엔지니어들에게 흥미로운 볼거리를 제공합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 가정 내에 고성능 서버를 구축할 때는 전력 소모량과 소음, 그리고 발열 관리를 위한 냉방 설비가 필수적으로 고려되어야 합니다.</t>
+    <t>본 영상은 테크 유튜버 'TECH WORLD'가 'うんちゃま'의 자택을 방문하여 일반 가정집에서는 보기 힘든 초대형 개인 서버실을 탐방하는 내용을 담고 있습니다. 전문가 수준으로 구축된 서버 환경을 공개하며 개인 서버 운용에 대한 흥미로운 사례를 보여줍니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 일반적인 가정용 환경을 넘어서는 대규모 서버 구축에는 고도의 냉각 시설과 전력 설계가 필수적이므로 주의가 필요합니다.</t>
   </si>
   <si>
     <t>【検証】新型「REDMAGIC 11”S” Pro」を購入。”怪しい動作”どうなった？</t>
@@ -629,10 +629,10 @@
     <t>さいちょう2nd</t>
   </si>
   <si>
-    <t>본 영상은 게이밍 스마트폰인 'REDMAGIC 9S Pro'의 검증기로, 이전 모델에서 제기되었던 기기 작동의 의문점들이 최신 모델에서 어떻게 개선되거나 변화했는지를 다루고 있습니다. 게임 성능 중심의 기기 특성을 고려하여 실제 사용 시의 안정성과 소프트웨어 최적화 상태를 사용자 관점에서 객관적으로 분석하는 내용을 담고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 기기 구매 전 의문이 드는 동작이나 소프트웨어 이슈가 있다면 공식 업데이트 기록이나 사용자 커뮤니티의 실사용 후기를 먼저 확인하는 것이 좋습니다.</t>
+    <t>본 영상은 게이밍 스마트폰인 'REDMAGIC 9S Pro'(영상 내 11S Pro로 언급)를 구매하여 이전 모델에서 지적되었던 이상 동작이나 소프트웨어적인 문제점들이 어떻게 개선되었는지 혹은 여전히 남아있는지 간략하게 검증하는 내용을 담고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 기기 성능 검증 영상은 제조사의 공식 사양과 실사용 시 발생하는 최적화 문제를 구분해서 파악하는 것이 중요합니다.</t>
   </si>
   <si>
     <t>溝口さんに「それ違います」と正直に伝えました</t>
@@ -644,10 +644,10 @@
     <t>1:05:52</t>
   </si>
   <si>
-    <t>야마토 리노가 기존 10만 구독자 메인 채널을 해킹당해 복구가 불투명해지자, 새로운 채널을 개설하며 구독을 간곡히 요청하는 영상입니다. 시청자들에게 신규 채널로의 이전과 구독을 부탁하며 향후 활동 재개 의지를 밝혔습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 채널 해킹 상황을 알리며 구독을 유도하는 방식의 영상이므로 콘텐츠의 진위 여부를 확인하며 시청하는 것이 좋습니다.</t>
+    <t>유튜버 야마토 리노가 운영하던 10만 구독자 규모의 메인 채널을 해킹당해 복구가 불투명한 상황임을 알리며, 시청자들에게 새로운 채널에 대한 구독과 응원을 간곡히 요청하는 영상입니다. 기존 채널의 상실을 알리고 새로운 출발을 위한 팬들의 결집을 유도하고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 갑작스러운 채널 해킹 상황을 알리는 클릭베이트성 홍보 영상일 수 있으니 채널의 진위 여부를 확인 후 구독하시기 바랍니다.</t>
   </si>
   <si>
     <t>【石川県金沢】酔った勢いで旅行したら、過去最悪の空気の旅行が仕上がりました。</t>
@@ -659,10 +659,10 @@
     <t>2:18:07</t>
   </si>
   <si>
-    <t>술기운에 충동적으로 떠난 이시카와현 가나자와 여행에서 예민하고 결벽증이 심한 사장 우지하라와 그를 놀리기 좋아하는 카메라맨 우에다, 친구 사카모토가 겪는 최악의 여행기를 담았습니다. 세 사람의 티격태격하는 갈등과 웃픈 상황이 반복되며, 준비되지 않은 즉흥 여행이 어떻게 파국으로 치닫는지 여과 없이 보여주는 코믹 다큐멘터리입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 계획 없는 충동 여행이 예민한 성격의 동행자와 만났을 때 벌어질 수 있는 최악의 상황을 다루고 있으니 여행 전 멤버 간의 성향 파악은 필수입니다.</t>
+    <t>술에 취한 상태로 이시카와현 가나자와 여행을 떠난 우지하라와 동료들의 기록입니다. 결벽증과 예민한 성격의 우지하라가 겪는 여행 중의 갈등과 소동을 담았으며, 평소 이들의 케미와는 다른 최악의 분위기로 치닫는 과정이 영상의 핵심입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 갈등 상황을 담은 여행 브이로그이므로, 출연진 간의 긴장감이나 무거운 분위기를 감안하고 시청하시길 바랍니다.</t>
   </si>
   <si>
     <t>라이징스타</t>
@@ -677,10 +677,10 @@
     <t>20:06</t>
   </si>
   <si>
-    <t>본 영상은 오타니 쇼헤이와 사사키 로키에 관한 최근 MLB 소식을 다룹니다. 다저스의 역전승 과정과 사사키 로키의 6실점 부진에 대한 현지 반응, 특히 경기 중 오타니가 보인 행동에 대한 프라이어 코치의 감명과 동료 선수들의 인터뷰 내용을 중심으로 오타니의 영향력을 집중 조명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 채널은 다수의 스포츠 채널이 사용하는 자극적인 클릭베이트 형식의 콘텐츠를 제공하므로 정보의 출처를 반드시 확인하시기 바랍니다.</t>
+    <t>본 영상은 오타니 쇼헤이와 사사키 로키의 최신 MLB 소식을 전하며, 다저스의 역전승과 사사키의 6실점 부진 상황을 다룹니다. 특히 사사키가 무너진 직후 오타니가 보인 발언이 프라이어 코치를 감동시켰다는 일화와 함께, 먼시, 베츠 등 팀 동료들과 전설적인 야구인들의 인터뷰를 통해 두 선수의 현재 상태를 분석하고 응원하는 내용을 담고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 채널은 오타니 관련 이슈를 자극적으로 재구성하는 콘텐츠가 많으므로, 구체적인 경기 결과나 공식 기록은 메이저리그 공식 홈페이지를 통해 재확인하는 것이 좋습니다.</t>
   </si>
   <si>
     <t>"홈런 폭격중인 한국 초특급 유망주" 콜업 후 8경기 5홈런에 MVP 선정되자 뒤집어진 미국 현지중계진 ㄷㄷ</t>
@@ -692,25 +692,10 @@
     <t>8:40</t>
   </si>
   <si>
-    <t>미국 마이너리그에서 활약 중인 한국 야구 유망주 조원빈 선수가 콜업 후 8경기에서 5개의 홈런을 몰아치며 MVP를 수상하는 압도적인 퍼포먼스를 선보였습니다. 이 소식에 현지 중계진들이 놀라움을 감추지 못하며 극찬을 보내고 있는 상황을 상세히 다루고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목과 썸네일에서 강조하는 '현지 중계진의 반응'은 조회수를 높이기 위한 과장된 자극적 표현이 포함되어 있을 수 있으니 객관적인 기록 위주로 시청하는 것이 좋습니다.</t>
-  </si>
-  <si>
-    <t>ケルチ連絡路が炎上…ロシアは最後の生命線を断たれる一撃に身構える</t>
-  </si>
-  <si>
-    <t>地政学の羅針盤</t>
-  </si>
-  <si>
-    <t>19:23</t>
-  </si>
-  <si>
-    <t>본 영상은 우크라이나가 크림반도를 잇는 핵심 보급로인 케르치 해협의 연료 및 수송 시설을 동시에 타격한 상황을 분석합니다. 러시아는 전방위적인 우크라이나의 압박으로 인해 방어 자원을 분산해야 하는 곤경에 처했으며, 이는 보급선 차단이 전쟁의 판도를 바꿀 수 있음을 시사합니다. 또한 이러한 군사적 흐름이 현대전과 섬나라 방위 전략에 주는 함의를 지정학적 관점에서 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 제목과 내용이 자극적인 군사 분석 영상이므로, 객관적인 군사 정세 파악을 위해 여러 소스의 교차 검증이 필요합니다.</t>
+    <t>미국 마이너리그에서 활약 중인 한국 야구 유망주 조원빈 선수가 콜업 이후 8경기에서 5개의 홈런을 터뜨리는 압도적인 퍼포먼스를 선보였습니다. 이로 인해 주간 MVP에 선정되는 등 현지 중계진과 팬들의 뜨거운 찬사를 받으며 메이저리그 진출 가능성을 한층 높이고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 썸네일과 제목으로 조원빈 선수의 활약을 극대화하여 표현한 영상이므로 객관적인 기록 위주로 사실관계를 확인하는 것이 좋습니다.</t>
   </si>
 </sst>
 </file>
@@ -1172,16 +1157,16 @@
         <v>22</v>
       </c>
       <c r="I2" s="3">
-        <v>1260514</v>
+        <v>1260589</v>
       </c>
       <c r="J2" s="3">
-        <v>20986</v>
+        <v>20988</v>
       </c>
       <c r="K2" s="3">
         <v>2327</v>
       </c>
       <c r="L2" s="3">
-        <v>123947</v>
+        <v>123886</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>23</v>
@@ -1222,16 +1207,16 @@
         <v>30</v>
       </c>
       <c r="I3" s="3">
-        <v>275930</v>
+        <v>276250</v>
       </c>
       <c r="J3" s="3">
-        <v>5812</v>
+        <v>5820</v>
       </c>
       <c r="K3" s="3">
-        <v>1909</v>
+        <v>1913</v>
       </c>
       <c r="L3" s="3">
-        <v>59652</v>
+        <v>59660</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>31</v>
@@ -1272,16 +1257,16 @@
         <v>35</v>
       </c>
       <c r="I4" s="3">
-        <v>271320</v>
+        <v>271870</v>
       </c>
       <c r="J4" s="3">
-        <v>4658</v>
+        <v>4664</v>
       </c>
       <c r="K4" s="3">
         <v>438</v>
       </c>
       <c r="L4" s="3">
-        <v>42506</v>
+        <v>42515</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>36</v>
@@ -1322,16 +1307,16 @@
         <v>42</v>
       </c>
       <c r="I5" s="3">
-        <v>732004</v>
+        <v>732316</v>
       </c>
       <c r="J5" s="3">
-        <v>18064</v>
+        <v>18067</v>
       </c>
       <c r="K5" s="3">
         <v>1455</v>
       </c>
       <c r="L5" s="3">
-        <v>101216</v>
+        <v>101158</v>
       </c>
       <c r="M5" s="4" t="s">
         <v>43</v>
@@ -1372,16 +1357,16 @@
         <v>48</v>
       </c>
       <c r="I6" s="3">
-        <v>248130</v>
+        <v>248168</v>
       </c>
       <c r="J6" s="3">
-        <v>8483</v>
+        <v>8485</v>
       </c>
       <c r="K6" s="3">
         <v>1072</v>
       </c>
       <c r="L6" s="3">
-        <v>61701</v>
+        <v>61598</v>
       </c>
       <c r="M6" s="4" t="s">
         <v>49</v>
@@ -1422,16 +1407,16 @@
         <v>53</v>
       </c>
       <c r="I7" s="3">
-        <v>331591</v>
+        <v>331766</v>
       </c>
       <c r="J7" s="3">
-        <v>5108</v>
+        <v>5111</v>
       </c>
       <c r="K7" s="3">
         <v>748</v>
       </c>
       <c r="L7" s="3">
-        <v>60873</v>
+        <v>60787</v>
       </c>
       <c r="M7" s="4" t="s">
         <v>54</v>
@@ -1472,16 +1457,16 @@
         <v>59</v>
       </c>
       <c r="I8" s="3">
-        <v>217667</v>
+        <v>217946</v>
       </c>
       <c r="J8" s="3">
-        <v>6442</v>
+        <v>6447</v>
       </c>
       <c r="K8" s="3">
         <v>511</v>
       </c>
       <c r="L8" s="3">
-        <v>47089</v>
+        <v>47047</v>
       </c>
       <c r="M8" s="4" t="s">
         <v>60</v>
@@ -1522,16 +1507,16 @@
         <v>65</v>
       </c>
       <c r="I9" s="3">
-        <v>65257</v>
+        <v>65562</v>
       </c>
       <c r="J9" s="3">
-        <v>2383</v>
+        <v>2399</v>
       </c>
       <c r="K9" s="3">
         <v>688</v>
       </c>
       <c r="L9" s="3">
-        <v>26552</v>
+        <v>26569</v>
       </c>
       <c r="M9" s="4" t="s">
         <v>66</v>
@@ -1572,16 +1557,16 @@
         <v>71</v>
       </c>
       <c r="I10" s="3">
-        <v>177026</v>
+        <v>22117</v>
       </c>
       <c r="J10" s="3">
-        <v>3863</v>
+        <v>1194</v>
       </c>
       <c r="K10" s="3">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="L10" s="3">
-        <v>20279</v>
+        <v>17590</v>
       </c>
       <c r="M10" s="4" t="s">
         <v>72</v>
@@ -1616,28 +1601,28 @@
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="3">
+        <v>650530</v>
+      </c>
+      <c r="J11" s="3">
+        <v>29698</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1802</v>
+      </c>
+      <c r="L11" s="3">
+        <v>301458</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="3">
-        <v>645961</v>
-      </c>
-      <c r="J11" s="3">
-        <v>29562</v>
-      </c>
-      <c r="K11" s="3">
-        <v>1799</v>
-      </c>
-      <c r="L11" s="3">
-        <v>301633</v>
-      </c>
-      <c r="M11" s="4" t="s">
+      <c r="N11" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>25</v>
@@ -1660,34 +1645,34 @@
         <v>2</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I12" s="3">
-        <v>1109175</v>
+        <v>1109726</v>
       </c>
       <c r="J12" s="3">
-        <v>9060</v>
+        <v>9061</v>
       </c>
       <c r="K12" s="3">
         <v>752</v>
       </c>
       <c r="L12" s="3">
-        <v>114431</v>
+        <v>114373</v>
       </c>
       <c r="M12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="N12" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>25</v>
@@ -1710,34 +1695,34 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="3">
+        <v>233809</v>
+      </c>
+      <c r="J13" s="3">
+        <v>4691</v>
+      </c>
+      <c r="K13" s="3">
+        <v>519</v>
+      </c>
+      <c r="L13" s="3">
+        <v>84731</v>
+      </c>
+      <c r="M13" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I13" s="3">
-        <v>233280</v>
-      </c>
-      <c r="J13" s="3">
-        <v>4687</v>
-      </c>
-      <c r="K13" s="3">
-        <v>517</v>
-      </c>
-      <c r="L13" s="3">
-        <v>85110</v>
-      </c>
-      <c r="M13" s="4" t="s">
+      <c r="N13" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>25</v>
@@ -1754,40 +1739,40 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="I14" s="3">
-        <v>711028</v>
+        <v>711094</v>
       </c>
       <c r="J14" s="3">
-        <v>6509</v>
+        <v>6511</v>
       </c>
       <c r="K14" s="3">
         <v>2471</v>
       </c>
       <c r="L14" s="3">
-        <v>79154</v>
+        <v>79107</v>
       </c>
       <c r="M14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="N14" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>25</v>
@@ -1804,40 +1789,40 @@
         <v>17</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="I15" s="3">
-        <v>464311</v>
+        <v>464356</v>
       </c>
       <c r="J15" s="3">
-        <v>18948</v>
+        <v>18949</v>
       </c>
       <c r="K15" s="3">
         <v>2223</v>
       </c>
       <c r="L15" s="3">
-        <v>40891</v>
+        <v>40886</v>
       </c>
       <c r="M15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="N15" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>25</v>
@@ -1854,40 +1839,40 @@
         <v>17</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="I16" s="3">
-        <v>120406</v>
+        <v>121040</v>
       </c>
       <c r="J16" s="3">
-        <v>1883</v>
+        <v>1893</v>
       </c>
       <c r="K16" s="3">
         <v>292</v>
       </c>
       <c r="L16" s="3">
-        <v>40118</v>
+        <v>40055</v>
       </c>
       <c r="M16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="N16" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>25</v>
@@ -1904,40 +1889,40 @@
         <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D17" s="2">
         <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3111877</v>
+      </c>
+      <c r="J17" s="3">
+        <v>67814</v>
+      </c>
+      <c r="K17" s="3">
+        <v>11370</v>
+      </c>
+      <c r="L17" s="3">
+        <v>660314</v>
+      </c>
+      <c r="M17" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="I17" s="3">
-        <v>3108714</v>
-      </c>
-      <c r="J17" s="3">
-        <v>67753</v>
-      </c>
-      <c r="K17" s="3">
-        <v>11357</v>
-      </c>
-      <c r="L17" s="3">
-        <v>660852</v>
-      </c>
-      <c r="M17" s="4" t="s">
+      <c r="N17" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>25</v>
@@ -1954,40 +1939,40 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D18" s="2">
         <v>2</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="3">
+        <v>3391075</v>
+      </c>
+      <c r="J18" s="3">
+        <v>42453</v>
+      </c>
+      <c r="K18" s="3">
+        <v>5870</v>
+      </c>
+      <c r="L18" s="3">
+        <v>406058</v>
+      </c>
+      <c r="M18" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="I18" s="3">
-        <v>3389152</v>
-      </c>
-      <c r="J18" s="3">
-        <v>42440</v>
-      </c>
-      <c r="K18" s="3">
-        <v>5869</v>
-      </c>
-      <c r="L18" s="3">
-        <v>406244</v>
-      </c>
-      <c r="M18" s="4" t="s">
+      <c r="N18" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="N18" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="O18" s="2" t="s">
         <v>25</v>
@@ -2004,40 +1989,40 @@
         <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1540377</v>
+      </c>
+      <c r="J19" s="3">
+        <v>32509</v>
+      </c>
+      <c r="K19" s="3">
+        <v>4248</v>
+      </c>
+      <c r="L19" s="3">
+        <v>310809</v>
+      </c>
+      <c r="M19" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="3">
-        <v>1538989</v>
-      </c>
-      <c r="J19" s="3">
-        <v>32482</v>
-      </c>
-      <c r="K19" s="3">
-        <v>4243</v>
-      </c>
-      <c r="L19" s="3">
-        <v>311099</v>
-      </c>
-      <c r="M19" s="4" t="s">
+      <c r="N19" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="N19" s="4" t="s">
-        <v>124</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>25</v>
@@ -2051,7 +2036,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>18</v>
@@ -2060,34 +2045,34 @@
         <v>1</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I20" s="3">
-        <v>184513</v>
+        <v>184552</v>
       </c>
       <c r="J20" s="3">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="K20" s="3">
         <v>289</v>
       </c>
       <c r="L20" s="3">
-        <v>23017</v>
+        <v>23001</v>
       </c>
       <c r="M20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="N20" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>25</v>
@@ -2101,7 +2086,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>18</v>
@@ -2110,16 +2095,16 @@
         <v>2</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="I21" s="3">
         <v>41596</v>
@@ -2131,13 +2116,13 @@
         <v>52</v>
       </c>
       <c r="L21" s="3">
-        <v>5195</v>
+        <v>5191</v>
       </c>
       <c r="M21" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>25</v>
@@ -2151,7 +2136,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>38</v>
@@ -2160,34 +2145,34 @@
         <v>1</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I22" s="3">
+        <v>496063</v>
+      </c>
+      <c r="J22" s="3">
+        <v>6577</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1762</v>
+      </c>
+      <c r="L22" s="3">
+        <v>67766</v>
+      </c>
+      <c r="M22" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="I22" s="3">
-        <v>495900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>6574</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1761</v>
-      </c>
-      <c r="L22" s="3">
-        <v>67802</v>
-      </c>
-      <c r="M22" s="4" t="s">
+      <c r="N22" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>25</v>
@@ -2201,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>38</v>
@@ -2210,34 +2195,34 @@
         <v>2</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I23" s="3">
+        <v>207355</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3361</v>
+      </c>
+      <c r="K23" s="3">
+        <v>218</v>
+      </c>
+      <c r="L23" s="3">
+        <v>35924</v>
+      </c>
+      <c r="M23" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="I23" s="3">
-        <v>207148</v>
-      </c>
-      <c r="J23" s="3">
-        <v>3358</v>
-      </c>
-      <c r="K23" s="3">
-        <v>216</v>
-      </c>
-      <c r="L23" s="3">
-        <v>35937</v>
-      </c>
-      <c r="M23" s="4" t="s">
+      <c r="N23" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>25</v>
@@ -2251,7 +2236,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>38</v>
@@ -2260,19 +2245,19 @@
         <v>3</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I24" s="3">
-        <v>206152</v>
+        <v>206249</v>
       </c>
       <c r="J24" s="3">
         <v>3692</v>
@@ -2281,13 +2266,13 @@
         <v>223</v>
       </c>
       <c r="L24" s="3">
-        <v>35928</v>
+        <v>35873</v>
       </c>
       <c r="M24" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="N24" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="N24" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>25</v>
@@ -2301,7 +2286,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>56</v>
@@ -2310,22 +2295,22 @@
         <v>1</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>41</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I25" s="3">
-        <v>30978</v>
+        <v>30999</v>
       </c>
       <c r="J25" s="3">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="K25" s="3">
         <v>81</v>
@@ -2334,10 +2319,10 @@
         <v>5354</v>
       </c>
       <c r="M25" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="N25" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>25</v>
@@ -2351,7 +2336,7 @@
         <v>16</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>56</v>
@@ -2360,34 +2345,34 @@
         <v>2</v>
       </c>
       <c r="E26" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I26" s="3">
-        <v>27370</v>
+        <v>27392</v>
       </c>
       <c r="J26" s="3">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="K26" s="3">
         <v>70</v>
       </c>
       <c r="L26" s="3">
-        <v>5068</v>
+        <v>5065</v>
       </c>
       <c r="M26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="N26" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>25</v>
@@ -2401,7 +2386,7 @@
         <v>16</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>56</v>
@@ -2410,34 +2395,34 @@
         <v>3</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I27" s="3">
-        <v>24085</v>
+        <v>24109</v>
       </c>
       <c r="J27" s="3">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K27" s="3">
         <v>34</v>
       </c>
       <c r="L27" s="3">
-        <v>4760</v>
+        <v>4757</v>
       </c>
       <c r="M27" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="N27" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>25</v>
@@ -2451,43 +2436,43 @@
         <v>16</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D28" s="2">
         <v>1</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="I28" s="3">
-        <v>2038495</v>
+        <v>2041784</v>
       </c>
       <c r="J28" s="3">
-        <v>74405</v>
+        <v>74423</v>
       </c>
       <c r="K28" s="3">
         <v>5204</v>
       </c>
       <c r="L28" s="3">
-        <v>293756</v>
+        <v>293818</v>
       </c>
       <c r="M28" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="N28" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>171</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>25</v>
@@ -2501,43 +2486,43 @@
         <v>16</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D29" s="2">
         <v>2</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="I29" s="3">
+        <v>483860</v>
+      </c>
+      <c r="J29" s="3">
+        <v>22970</v>
+      </c>
+      <c r="K29" s="3">
+        <v>1797</v>
+      </c>
+      <c r="L29" s="3">
+        <v>76753</v>
+      </c>
+      <c r="M29" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="I29" s="3">
-        <v>483348</v>
-      </c>
-      <c r="J29" s="3">
-        <v>22957</v>
-      </c>
-      <c r="K29" s="3">
-        <v>1796</v>
-      </c>
-      <c r="L29" s="3">
-        <v>76741</v>
-      </c>
-      <c r="M29" s="4" t="s">
+      <c r="N29" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>25</v>
@@ -2551,7 +2536,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>74</v>
@@ -2560,34 +2545,34 @@
         <v>1</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>47</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I30" s="3">
+        <v>1785669</v>
+      </c>
+      <c r="J30" s="3">
+        <v>48007</v>
+      </c>
+      <c r="K30" s="3">
+        <v>4399</v>
+      </c>
+      <c r="L30" s="3">
+        <v>375279</v>
+      </c>
+      <c r="M30" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="I30" s="3">
-        <v>1783117</v>
-      </c>
-      <c r="J30" s="3">
-        <v>47972</v>
-      </c>
-      <c r="K30" s="3">
-        <v>4398</v>
-      </c>
-      <c r="L30" s="3">
-        <v>375570</v>
-      </c>
-      <c r="M30" s="4" t="s">
+      <c r="N30" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>181</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>25</v>
@@ -2601,7 +2586,7 @@
         <v>16</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>74</v>
@@ -2610,34 +2595,34 @@
         <v>2</v>
       </c>
       <c r="E31" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="3">
+        <v>640223</v>
+      </c>
+      <c r="J31" s="3">
+        <v>23823</v>
+      </c>
+      <c r="K31" s="3">
+        <v>1016</v>
+      </c>
+      <c r="L31" s="3">
+        <v>243392</v>
+      </c>
+      <c r="M31" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="I31" s="3">
-        <v>636723</v>
-      </c>
-      <c r="J31" s="3">
-        <v>23756</v>
-      </c>
-      <c r="K31" s="3">
-        <v>1013</v>
-      </c>
-      <c r="L31" s="3">
-        <v>243647</v>
-      </c>
-      <c r="M31" s="4" t="s">
+      <c r="N31" s="4" t="s">
         <v>185</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>186</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>25</v>
@@ -2651,7 +2636,7 @@
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>74</v>
@@ -2660,34 +2645,34 @@
         <v>3</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I32" s="3">
-        <v>511786</v>
+        <v>512607</v>
       </c>
       <c r="J32" s="3">
-        <v>15362</v>
+        <v>15376</v>
       </c>
       <c r="K32" s="3">
         <v>968</v>
       </c>
       <c r="L32" s="3">
-        <v>129779</v>
+        <v>129594</v>
       </c>
       <c r="M32" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="N32" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>25</v>
@@ -2701,37 +2686,37 @@
         <v>16</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D33" s="2">
         <v>1</v>
       </c>
       <c r="E33" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="G33" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>194</v>
       </c>
       <c r="I33" s="3">
-        <v>335249</v>
+        <v>335311</v>
       </c>
       <c r="J33" s="3">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="K33" s="3">
         <v>35</v>
       </c>
       <c r="L33" s="3">
-        <v>31824</v>
+        <v>31802</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>195</v>
@@ -2751,10 +2736,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D34" s="2">
         <v>2</v>
@@ -2766,22 +2751,22 @@
         <v>198</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>199</v>
       </c>
       <c r="I34" s="3">
-        <v>197814</v>
+        <v>197907</v>
       </c>
       <c r="J34" s="3">
-        <v>2866</v>
+        <v>2867</v>
       </c>
       <c r="K34" s="3">
         <v>154</v>
       </c>
       <c r="L34" s="3">
-        <v>20908</v>
+        <v>20900</v>
       </c>
       <c r="M34" s="4" t="s">
         <v>200</v>
@@ -2801,10 +2786,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D35" s="2">
         <v>3</v>
@@ -2816,7 +2801,7 @@
         <v>203</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>48</v>
@@ -2831,7 +2816,7 @@
         <v>568</v>
       </c>
       <c r="L35" s="3">
-        <v>20158</v>
+        <v>20144</v>
       </c>
       <c r="M35" s="4" t="s">
         <v>204</v>
@@ -2851,10 +2836,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D36" s="2">
         <v>1</v>
@@ -2872,16 +2857,16 @@
         <v>208</v>
       </c>
       <c r="I36" s="3">
-        <v>1471602</v>
+        <v>1474575</v>
       </c>
       <c r="J36" s="3">
-        <v>26227</v>
+        <v>26258</v>
       </c>
       <c r="K36" s="3">
-        <v>11678</v>
+        <v>11692</v>
       </c>
       <c r="L36" s="3">
-        <v>457644</v>
+        <v>457111</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>209</v>
@@ -2901,10 +2886,10 @@
         <v>16</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D37" s="2">
         <v>2</v>
@@ -2922,16 +2907,16 @@
         <v>213</v>
       </c>
       <c r="I37" s="3">
-        <v>1326768</v>
+        <v>1332463</v>
       </c>
       <c r="J37" s="3">
-        <v>30026</v>
+        <v>30081</v>
       </c>
       <c r="K37" s="3">
-        <v>3094</v>
+        <v>3098</v>
       </c>
       <c r="L37" s="3">
-        <v>373443</v>
+        <v>373278</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>214</v>
@@ -2991,7 +2976,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3049,7 +3034,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>216</v>
@@ -3064,13 +3049,13 @@
         <v>218</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>219</v>
       </c>
       <c r="I2" s="3">
-        <v>123236</v>
+        <v>123261</v>
       </c>
       <c r="J2" s="3">
         <v>480</v>
@@ -3114,16 +3099,16 @@
         <v>223</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>224</v>
       </c>
       <c r="I3" s="3">
-        <v>83685</v>
+        <v>84048</v>
       </c>
       <c r="J3" s="3">
-        <v>908</v>
+        <v>914</v>
       </c>
       <c r="K3" s="3">
         <v>31</v>
@@ -3141,56 +3126,6 @@
         <v>25</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D4" s="2">
-        <v>3</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="I4" s="3">
-        <v>77998</v>
-      </c>
-      <c r="J4" s="3">
-        <v>681</v>
-      </c>
-      <c r="K4" s="3">
-        <v>17</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3198,7 +3133,6 @@
   <hyperlinks>
     <hyperlink ref="O2" r:id="rId1"/>
     <hyperlink ref="O3" r:id="rId2"/>
-    <hyperlink ref="O4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
